--- a/database/event/8038/event_8038_evp_summary.xlsx
+++ b/database/event/8038/event_8038_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>11.4859</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>7.2368</v>
       </c>
       <c r="D2" t="n">
         <v>4.2187</v>
@@ -545,7 +545,7 @@
         <v>6.5942</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>4.1547</v>
       </c>
       <c r="D3" t="n">
         <v>2.2425</v>
@@ -591,7 +591,7 @@
         <v>6.5664</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>4.1372</v>
       </c>
       <c r="D4" t="n">
         <v>2.2313</v>
@@ -637,7 +637,7 @@
         <v>5.7744</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>3.6382</v>
       </c>
       <c r="D5" t="n">
         <v>1.9114</v>
@@ -683,7 +683,7 @@
         <v>5.1775</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>3.2621</v>
       </c>
       <c r="D6" t="n">
         <v>1.6702</v>
@@ -729,7 +729,7 @@
         <v>5.1713</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>3.2582</v>
       </c>
       <c r="D7" t="n">
         <v>1.6677</v>
@@ -775,7 +775,7 @@
         <v>4.9811</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>3.1384</v>
       </c>
       <c r="D8" t="n">
         <v>1.5909</v>
@@ -821,7 +821,7 @@
         <v>4.9174</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>3.0982</v>
       </c>
       <c r="D9" t="n">
         <v>1.5652</v>
@@ -867,7 +867,7 @@
         <v>4.3902</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2.7661</v>
       </c>
       <c r="D10" t="n">
         <v>1.3522</v>
@@ -913,7 +913,7 @@
         <v>4.1813</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>2.6345</v>
       </c>
       <c r="D11" t="n">
         <v>1.2678</v>
@@ -959,7 +959,7 @@
         <v>4.1461</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>2.6123</v>
       </c>
       <c r="D12" t="n">
         <v>1.2536</v>
@@ -1005,7 +1005,7 @@
         <v>4.1033</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>2.5853</v>
       </c>
       <c r="D13" t="n">
         <v>1.2363</v>
@@ -1051,7 +1051,7 @@
         <v>3.16</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1.991</v>
       </c>
       <c r="D14" t="n">
         <v>0.8552</v>
@@ -1097,7 +1097,7 @@
         <v>3.1218</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1.9669</v>
       </c>
       <c r="D15" t="n">
         <v>0.8398</v>
@@ -1143,7 +1143,7 @@
         <v>3.015</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1.8996</v>
       </c>
       <c r="D16" t="n">
         <v>0.7966</v>
@@ -1189,7 +1189,7 @@
         <v>3.005</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1.8933</v>
       </c>
       <c r="D17" t="n">
         <v>0.7926</v>
@@ -1235,7 +1235,7 @@
         <v>2.893</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1.8228</v>
       </c>
       <c r="D18" t="n">
         <v>0.7473</v>
@@ -1281,7 +1281,7 @@
         <v>2.8789</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1.8139</v>
       </c>
       <c r="D19" t="n">
         <v>0.7416</v>
@@ -1327,7 +1327,7 @@
         <v>2.7078</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1.7061</v>
       </c>
       <c r="D20" t="n">
         <v>0.6725</v>
@@ -1373,7 +1373,7 @@
         <v>2.6407</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1.6638</v>
       </c>
       <c r="D21" t="n">
         <v>0.6454</v>
@@ -1419,7 +1419,7 @@
         <v>2.6336</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1.6593</v>
       </c>
       <c r="D22" t="n">
         <v>0.6425999999999999</v>
@@ -1465,7 +1465,7 @@
         <v>2.2298</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1.4049</v>
       </c>
       <c r="D23" t="n">
         <v>0.4794</v>
@@ -1511,7 +1511,7 @@
         <v>2.0904</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1.3171</v>
       </c>
       <c r="D24" t="n">
         <v>0.4231</v>
@@ -1557,7 +1557,7 @@
         <v>1.9318</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1.2171</v>
       </c>
       <c r="D25" t="n">
         <v>0.359</v>
@@ -1603,7 +1603,7 @@
         <v>1.876</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1.182</v>
       </c>
       <c r="D26" t="n">
         <v>0.3365</v>
@@ -1649,7 +1649,7 @@
         <v>1.8449</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1.1624</v>
       </c>
       <c r="D27" t="n">
         <v>0.3239</v>
@@ -1695,7 +1695,7 @@
         <v>1.7962</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1.1317</v>
       </c>
       <c r="D28" t="n">
         <v>0.3043</v>
@@ -1741,7 +1741,7 @@
         <v>1.7591</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>1.1083</v>
       </c>
       <c r="D29" t="n">
         <v>0.2893</v>
@@ -1787,7 +1787,7 @@
         <v>1.7562</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1.1065</v>
       </c>
       <c r="D30" t="n">
         <v>0.2881</v>
@@ -1833,7 +1833,7 @@
         <v>1.7418</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>1.0974</v>
       </c>
       <c r="D31" t="n">
         <v>0.2823</v>
@@ -1879,7 +1879,7 @@
         <v>1.7164</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>1.0814</v>
       </c>
       <c r="D32" t="n">
         <v>0.272</v>
@@ -1925,7 +1925,7 @@
         <v>1.557</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.981</v>
       </c>
       <c r="D33" t="n">
         <v>0.2076</v>
@@ -1971,7 +1971,7 @@
         <v>1.5435</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.9725</v>
       </c>
       <c r="D34" t="n">
         <v>0.2022</v>
@@ -2017,7 +2017,7 @@
         <v>1.5349</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.9671</v>
       </c>
       <c r="D35" t="n">
         <v>0.1987</v>
@@ -2063,7 +2063,7 @@
         <v>1.3939</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.8782</v>
       </c>
       <c r="D36" t="n">
         <v>0.1417</v>
@@ -2109,7 +2109,7 @@
         <v>1.3614</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.8578</v>
       </c>
       <c r="D37" t="n">
         <v>0.1286</v>
@@ -2155,7 +2155,7 @@
         <v>1.3162</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.8293</v>
       </c>
       <c r="D38" t="n">
         <v>0.1104</v>
@@ -2201,7 +2201,7 @@
         <v>1.316</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.8292</v>
       </c>
       <c r="D39" t="n">
         <v>0.1103</v>
@@ -2247,7 +2247,7 @@
         <v>1.2741</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.8028</v>
       </c>
       <c r="D40" t="n">
         <v>0.09329999999999999</v>
@@ -2293,7 +2293,7 @@
         <v>1.2574</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.7922</v>
       </c>
       <c r="D41" t="n">
         <v>0.0866</v>
@@ -2339,7 +2339,7 @@
         <v>1.1949</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.7529</v>
       </c>
       <c r="D42" t="n">
         <v>0.0614</v>
@@ -2385,7 +2385,7 @@
         <v>1.0229</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.6445</v>
       </c>
       <c r="D43" t="n">
         <v>-0.0081</v>
@@ -2431,7 +2431,7 @@
         <v>0.6092</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.3838</v>
       </c>
       <c r="D44" t="n">
         <v>-0.1753</v>
@@ -2477,7 +2477,7 @@
         <v>0.5223</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.3291</v>
       </c>
       <c r="D45" t="n">
         <v>-0.2104</v>
@@ -2523,7 +2523,7 @@
         <v>0.5062</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.3189</v>
       </c>
       <c r="D46" t="n">
         <v>-0.2169</v>
@@ -2569,7 +2569,7 @@
         <v>0.2961</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.1866</v>
       </c>
       <c r="D47" t="n">
         <v>-0.3017</v>
@@ -2615,7 +2615,7 @@
         <v>0.2481</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.1563</v>
       </c>
       <c r="D48" t="n">
         <v>-0.3211</v>
@@ -2661,7 +2661,7 @@
         <v>0.2335</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.1471</v>
       </c>
       <c r="D49" t="n">
         <v>-0.327</v>
@@ -2707,7 +2707,7 @@
         <v>0.2191</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>0.138</v>
       </c>
       <c r="D50" t="n">
         <v>-0.3329</v>
@@ -2753,7 +2753,7 @@
         <v>0.1932</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>0.1217</v>
       </c>
       <c r="D51" t="n">
         <v>-0.3433</v>
@@ -2799,7 +2799,7 @@
         <v>0.0819</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>0.0516</v>
       </c>
       <c r="D52" t="n">
         <v>-0.3883</v>
@@ -2845,7 +2845,7 @@
         <v>0.0285</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="D53" t="n">
         <v>-0.4098</v>
@@ -2891,7 +2891,7 @@
         <v>-0.1429</v>
       </c>
       <c r="C54" t="n">
-        <v>-0</v>
+        <v>-0.09</v>
       </c>
       <c r="D54" t="n">
         <v>-0.4791</v>
@@ -2937,7 +2937,7 @@
         <v>-0.2172</v>
       </c>
       <c r="C55" t="n">
-        <v>-0</v>
+        <v>-0.1368</v>
       </c>
       <c r="D55" t="n">
         <v>-0.5091</v>
@@ -2983,7 +2983,7 @@
         <v>-0.2379</v>
       </c>
       <c r="C56" t="n">
-        <v>-0</v>
+        <v>-0.1499</v>
       </c>
       <c r="D56" t="n">
         <v>-0.5175</v>
@@ -3029,7 +3029,7 @@
         <v>-0.361</v>
       </c>
       <c r="C57" t="n">
-        <v>-0</v>
+        <v>-0.2274</v>
       </c>
       <c r="D57" t="n">
         <v>-0.5672</v>
@@ -3075,7 +3075,7 @@
         <v>-0.3993</v>
       </c>
       <c r="C58" t="n">
-        <v>-0</v>
+        <v>-0.2516</v>
       </c>
       <c r="D58" t="n">
         <v>-0.5827</v>
@@ -3121,7 +3121,7 @@
         <v>-0.4276</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.2694</v>
       </c>
       <c r="D59" t="n">
         <v>-0.5941</v>
@@ -3167,7 +3167,7 @@
         <v>-0.4662</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.2937</v>
       </c>
       <c r="D60" t="n">
         <v>-0.6097</v>
@@ -3213,7 +3213,7 @@
         <v>-0.6098</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.3842</v>
       </c>
       <c r="D61" t="n">
         <v>-0.6677</v>
@@ -3259,7 +3259,7 @@
         <v>-0.6777</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.427</v>
       </c>
       <c r="D62" t="n">
         <v>-0.6951000000000001</v>
@@ -3305,7 +3305,7 @@
         <v>-0.7010999999999999</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.4417</v>
       </c>
       <c r="D63" t="n">
         <v>-0.7046</v>
@@ -3351,7 +3351,7 @@
         <v>-1.0765</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.6783</v>
       </c>
       <c r="D64" t="n">
         <v>-0.8562</v>
@@ -3397,7 +3397,7 @@
         <v>-1.0897</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.6866</v>
       </c>
       <c r="D65" t="n">
         <v>-0.8616</v>
@@ -3443,7 +3443,7 @@
         <v>-1.2991</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.8185</v>
       </c>
       <c r="D66" t="n">
         <v>-0.9462</v>
@@ -3489,7 +3489,7 @@
         <v>-1.3005</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.8194</v>
       </c>
       <c r="D67" t="n">
         <v>-0.9467</v>
@@ -3535,7 +3535,7 @@
         <v>-1.4313</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.9018</v>
       </c>
       <c r="D68" t="n">
         <v>-0.9996</v>
@@ -3581,7 +3581,7 @@
         <v>-1.4426</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.9089</v>
       </c>
       <c r="D69" t="n">
         <v>-1.0041</v>
@@ -3627,7 +3627,7 @@
         <v>-1.463</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.9218</v>
       </c>
       <c r="D70" t="n">
         <v>-1.0124</v>
@@ -3673,7 +3673,7 @@
         <v>-1.5639</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-0.9853</v>
       </c>
       <c r="D71" t="n">
         <v>-1.0531</v>
@@ -3719,7 +3719,7 @@
         <v>-1.6008</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-1.0086</v>
       </c>
       <c r="D72" t="n">
         <v>-1.068</v>
@@ -3765,7 +3765,7 @@
         <v>-1.6707</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-1.0526</v>
       </c>
       <c r="D73" t="n">
         <v>-1.0963</v>
@@ -3811,7 +3811,7 @@
         <v>-1.6964</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-1.0688</v>
       </c>
       <c r="D74" t="n">
         <v>-1.1067</v>
@@ -3857,7 +3857,7 @@
         <v>-1.91</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-1.2034</v>
       </c>
       <c r="D75" t="n">
         <v>-1.193</v>
@@ -3903,7 +3903,7 @@
         <v>-1.9648</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-1.2379</v>
       </c>
       <c r="D76" t="n">
         <v>-1.2151</v>
@@ -3949,7 +3949,7 @@
         <v>-2.3407</v>
       </c>
       <c r="C77" t="n">
-        <v>-0</v>
+        <v>-1.4748</v>
       </c>
       <c r="D77" t="n">
         <v>-1.367</v>
@@ -3995,7 +3995,7 @@
         <v>-2.7187</v>
       </c>
       <c r="C78" t="n">
-        <v>-0</v>
+        <v>-1.7129</v>
       </c>
       <c r="D78" t="n">
         <v>-1.5197</v>
@@ -4041,7 +4041,7 @@
         <v>-2.8038</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-1.7665</v>
       </c>
       <c r="D79" t="n">
         <v>-1.554</v>
@@ -4087,7 +4087,7 @@
         <v>-3.1937</v>
       </c>
       <c r="C80" t="n">
-        <v>-0</v>
+        <v>-2.0122</v>
       </c>
       <c r="D80" t="n">
         <v>-1.7115</v>
@@ -4133,7 +4133,7 @@
         <v>-3.4179</v>
       </c>
       <c r="C81" t="n">
-        <v>-0</v>
+        <v>-2.1535</v>
       </c>
       <c r="D81" t="n">
         <v>-1.8021</v>

--- a/database/event/8038/event_8038_evp_summary.xlsx
+++ b/database/event/8038/event_8038_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>7.2368</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2187</v>
+        <v>4.1321</v>
       </c>
       <c r="E2" t="n">
         <v>11.4859</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.5942</v>
+        <v>6.5669</v>
       </c>
       <c r="C3" t="n">
-        <v>4.1547</v>
+        <v>4.1375</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2425</v>
+        <v>2.1723</v>
       </c>
       <c r="E3" t="n">
-        <v>6.5942</v>
+        <v>6.5669</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6659</v>
+        <v>3.6386</v>
       </c>
       <c r="G3" t="n">
         <v>2.9283</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6659</v>
+        <v>3.6386</v>
       </c>
       <c r="I3" t="n">
         <v>3.7001</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.5664</v>
+        <v>6.5571</v>
       </c>
       <c r="C4" t="n">
-        <v>4.1372</v>
+        <v>4.1313</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2313</v>
+        <v>2.1684</v>
       </c>
       <c r="E4" t="n">
-        <v>6.5664</v>
+        <v>6.5571</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4861</v>
+        <v>2.4768</v>
       </c>
       <c r="G4" t="n">
         <v>4.0803</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4861</v>
+        <v>2.4768</v>
       </c>
       <c r="I4" t="n">
         <v>2.4977</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.7744</v>
+        <v>5.7508</v>
       </c>
       <c r="C5" t="n">
-        <v>3.6382</v>
+        <v>3.6233</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9114</v>
+        <v>1.8472</v>
       </c>
       <c r="E5" t="n">
-        <v>5.7744</v>
+        <v>5.7508</v>
       </c>
       <c r="F5" t="n">
-        <v>4.6324</v>
+        <v>4.6088</v>
       </c>
       <c r="G5" t="n">
         <v>1.142</v>
       </c>
       <c r="H5" t="n">
-        <v>4.9605</v>
+        <v>4.9235</v>
       </c>
       <c r="I5" t="n">
         <v>5.0068</v>
@@ -686,7 +686,7 @@
         <v>3.2621</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6702</v>
+        <v>1.6188</v>
       </c>
       <c r="E6" t="n">
         <v>5.1775</v>
@@ -732,7 +732,7 @@
         <v>3.2582</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6677</v>
+        <v>1.6163</v>
       </c>
       <c r="E7" t="n">
         <v>5.1713</v>
@@ -772,25 +772,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.9811</v>
+        <v>4.9526</v>
       </c>
       <c r="C8" t="n">
-        <v>3.1384</v>
+        <v>3.1204</v>
       </c>
       <c r="D8" t="n">
-        <v>1.5909</v>
+        <v>1.5292</v>
       </c>
       <c r="E8" t="n">
-        <v>4.9811</v>
+        <v>4.9526</v>
       </c>
       <c r="F8" t="n">
-        <v>3.8217</v>
+        <v>3.7932</v>
       </c>
       <c r="G8" t="n">
         <v>1.1594</v>
       </c>
       <c r="H8" t="n">
-        <v>3.8217</v>
+        <v>3.7932</v>
       </c>
       <c r="I8" t="n">
         <v>3.8573</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.9174</v>
+        <v>4.8974</v>
       </c>
       <c r="C9" t="n">
-        <v>3.0982</v>
+        <v>3.0856</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5652</v>
+        <v>1.5072</v>
       </c>
       <c r="E9" t="n">
-        <v>4.9174</v>
+        <v>4.8974</v>
       </c>
       <c r="F9" t="n">
-        <v>4.1526</v>
+        <v>4.1326</v>
       </c>
       <c r="G9" t="n">
         <v>0.7648</v>
       </c>
       <c r="H9" t="n">
-        <v>4.2082</v>
+        <v>4.1769</v>
       </c>
       <c r="I9" t="n">
         <v>4.2475</v>
@@ -870,7 +870,7 @@
         <v>2.7661</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3522</v>
+        <v>1.3051</v>
       </c>
       <c r="E10" t="n">
         <v>4.3902</v>
@@ -916,7 +916,7 @@
         <v>2.6345</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2678</v>
+        <v>1.2219</v>
       </c>
       <c r="E11" t="n">
         <v>4.1813</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.1461</v>
+        <v>4.1361</v>
       </c>
       <c r="C12" t="n">
-        <v>2.6123</v>
+        <v>2.606</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2536</v>
+        <v>1.2039</v>
       </c>
       <c r="E12" t="n">
-        <v>4.1461</v>
+        <v>4.1361</v>
       </c>
       <c r="F12" t="n">
-        <v>4.1461</v>
+        <v>4.1361</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>4.198</v>
+        <v>4.1824</v>
       </c>
       <c r="I12" t="n">
         <v>4.2176</v>
@@ -1002,25 +1002,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.1033</v>
+        <v>4.0834</v>
       </c>
       <c r="C13" t="n">
-        <v>2.5853</v>
+        <v>2.5728</v>
       </c>
       <c r="D13" t="n">
-        <v>1.2363</v>
+        <v>1.1829</v>
       </c>
       <c r="E13" t="n">
-        <v>4.1033</v>
+        <v>4.0834</v>
       </c>
       <c r="F13" t="n">
-        <v>4.1439</v>
+        <v>4.124</v>
       </c>
       <c r="G13" t="n">
         <v>-0.0406</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1946</v>
+        <v>4.1634</v>
       </c>
       <c r="I13" t="n">
         <v>4.2337</v>
@@ -1054,7 +1054,7 @@
         <v>1.991</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8552</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="E14" t="n">
         <v>3.16</v>
@@ -1100,7 +1100,7 @@
         <v>1.9669</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8398</v>
+        <v>0.7998</v>
       </c>
       <c r="E15" t="n">
         <v>3.1218</v>
@@ -1146,7 +1146,7 @@
         <v>1.8996</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7966</v>
+        <v>0.7573</v>
       </c>
       <c r="E16" t="n">
         <v>3.015</v>
@@ -1192,7 +1192,7 @@
         <v>1.8933</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7926</v>
+        <v>0.7533</v>
       </c>
       <c r="E17" t="n">
         <v>3.005</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.893</v>
+        <v>2.8822</v>
       </c>
       <c r="C18" t="n">
-        <v>1.8228</v>
+        <v>1.8159</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7473</v>
+        <v>0.7044</v>
       </c>
       <c r="E18" t="n">
-        <v>2.893</v>
+        <v>2.8822</v>
       </c>
       <c r="F18" t="n">
-        <v>2.893</v>
+        <v>2.8822</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.893</v>
+        <v>2.8822</v>
       </c>
       <c r="I18" t="n">
         <v>2.9065</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.8789</v>
+        <v>2.8744</v>
       </c>
       <c r="C19" t="n">
-        <v>1.8139</v>
+        <v>1.811</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7416</v>
+        <v>0.7013</v>
       </c>
       <c r="E19" t="n">
-        <v>2.8789</v>
+        <v>2.8744</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2181</v>
+        <v>1.2136</v>
       </c>
       <c r="G19" t="n">
         <v>1.6608</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2181</v>
+        <v>1.2136</v>
       </c>
       <c r="I19" t="n">
         <v>1.2238</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.7078</v>
+        <v>2.683</v>
       </c>
       <c r="C20" t="n">
-        <v>1.7061</v>
+        <v>1.6904</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6725</v>
+        <v>0.625</v>
       </c>
       <c r="E20" t="n">
-        <v>2.7078</v>
+        <v>2.683</v>
       </c>
       <c r="F20" t="n">
-        <v>3.331</v>
+        <v>3.3062</v>
       </c>
       <c r="G20" t="n">
         <v>-0.6232</v>
       </c>
       <c r="H20" t="n">
-        <v>3.331</v>
+        <v>3.3062</v>
       </c>
       <c r="I20" t="n">
         <v>3.362</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.6407</v>
+        <v>2.6393</v>
       </c>
       <c r="C21" t="n">
-        <v>1.6638</v>
+        <v>1.6629</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6454</v>
+        <v>0.6076</v>
       </c>
       <c r="E21" t="n">
-        <v>2.6407</v>
+        <v>2.6393</v>
       </c>
       <c r="F21" t="n">
-        <v>0.188</v>
+        <v>0.1866</v>
       </c>
       <c r="G21" t="n">
         <v>2.4526</v>
       </c>
       <c r="H21" t="n">
-        <v>0.188</v>
+        <v>0.1866</v>
       </c>
       <c r="I21" t="n">
         <v>0.1898</v>
@@ -1416,25 +1416,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.6336</v>
+        <v>2.6135</v>
       </c>
       <c r="C22" t="n">
-        <v>1.6593</v>
+        <v>1.6466</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6425999999999999</v>
+        <v>0.5973000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>2.6336</v>
+        <v>2.6135</v>
       </c>
       <c r="F22" t="n">
-        <v>2.696</v>
+        <v>2.6759</v>
       </c>
       <c r="G22" t="n">
         <v>-0.0624</v>
       </c>
       <c r="H22" t="n">
-        <v>2.696</v>
+        <v>2.6759</v>
       </c>
       <c r="I22" t="n">
         <v>2.7211</v>
@@ -1468,7 +1468,7 @@
         <v>1.4049</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4794</v>
+        <v>0.4444</v>
       </c>
       <c r="E23" t="n">
         <v>2.2298</v>
@@ -1514,7 +1514,7 @@
         <v>1.3171</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4231</v>
+        <v>0.3889</v>
       </c>
       <c r="E24" t="n">
         <v>2.0904</v>
@@ -1560,7 +1560,7 @@
         <v>1.2171</v>
       </c>
       <c r="D25" t="n">
-        <v>0.359</v>
+        <v>0.3257</v>
       </c>
       <c r="E25" t="n">
         <v>1.9318</v>
@@ -1606,7 +1606,7 @@
         <v>1.182</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3365</v>
+        <v>0.3035</v>
       </c>
       <c r="E26" t="n">
         <v>1.876</v>
@@ -1652,7 +1652,7 @@
         <v>1.1624</v>
       </c>
       <c r="D27" t="n">
-        <v>0.3239</v>
+        <v>0.2911</v>
       </c>
       <c r="E27" t="n">
         <v>1.8449</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.7962</v>
+        <v>1.7951</v>
       </c>
       <c r="C28" t="n">
-        <v>1.1317</v>
+        <v>1.131</v>
       </c>
       <c r="D28" t="n">
-        <v>0.3043</v>
+        <v>0.2713</v>
       </c>
       <c r="E28" t="n">
-        <v>1.7962</v>
+        <v>1.7951</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2764</v>
+        <v>0.2754</v>
       </c>
       <c r="G28" t="n">
         <v>1.5197</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2764</v>
+        <v>0.2754</v>
       </c>
       <c r="I28" t="n">
         <v>0.2777</v>
@@ -1744,7 +1744,7 @@
         <v>1.1083</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2893</v>
+        <v>0.2569</v>
       </c>
       <c r="E29" t="n">
         <v>1.7591</v>
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.7562</v>
+        <v>1.7496</v>
       </c>
       <c r="C30" t="n">
-        <v>1.1065</v>
+        <v>1.1023</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2881</v>
+        <v>0.2531</v>
       </c>
       <c r="E30" t="n">
-        <v>1.7562</v>
+        <v>1.7496</v>
       </c>
       <c r="F30" t="n">
-        <v>1.7562</v>
+        <v>1.7496</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.7562</v>
+        <v>1.7496</v>
       </c>
       <c r="I30" t="n">
         <v>1.7644</v>
@@ -1836,7 +1836,7 @@
         <v>1.0974</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2823</v>
+        <v>0.25</v>
       </c>
       <c r="E31" t="n">
         <v>1.7418</v>
@@ -1882,7 +1882,7 @@
         <v>1.0814</v>
       </c>
       <c r="D32" t="n">
-        <v>0.272</v>
+        <v>0.2399</v>
       </c>
       <c r="E32" t="n">
         <v>1.7164</v>
@@ -1928,7 +1928,7 @@
         <v>0.981</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2076</v>
+        <v>0.1764</v>
       </c>
       <c r="E33" t="n">
         <v>1.557</v>
@@ -1974,7 +1974,7 @@
         <v>0.9725</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2022</v>
+        <v>0.171</v>
       </c>
       <c r="E34" t="n">
         <v>1.5435</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.5349</v>
+        <v>1.5319</v>
       </c>
       <c r="C35" t="n">
-        <v>0.9671</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1987</v>
+        <v>0.1664</v>
       </c>
       <c r="E35" t="n">
-        <v>1.5349</v>
+        <v>1.5319</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8134</v>
+        <v>0.8104</v>
       </c>
       <c r="G35" t="n">
         <v>0.7215</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8134</v>
+        <v>0.8104</v>
       </c>
       <c r="I35" t="n">
         <v>0.8172</v>
@@ -2066,7 +2066,7 @@
         <v>0.8782</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1417</v>
+        <v>0.1114</v>
       </c>
       <c r="E36" t="n">
         <v>1.3939</v>
@@ -2112,7 +2112,7 @@
         <v>0.8578</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1286</v>
+        <v>0.0985</v>
       </c>
       <c r="E37" t="n">
         <v>1.3614</v>
@@ -2158,7 +2158,7 @@
         <v>0.8293</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1104</v>
+        <v>0.0805</v>
       </c>
       <c r="E38" t="n">
         <v>1.3162</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.316</v>
+        <v>1.3064</v>
       </c>
       <c r="C39" t="n">
-        <v>0.8292</v>
+        <v>0.8231000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1103</v>
+        <v>0.0766</v>
       </c>
       <c r="E39" t="n">
-        <v>1.316</v>
+        <v>1.3064</v>
       </c>
       <c r="F39" t="n">
-        <v>2.5722</v>
+        <v>2.5626</v>
       </c>
       <c r="G39" t="n">
         <v>-1.2562</v>
       </c>
       <c r="H39" t="n">
-        <v>2.5722</v>
+        <v>2.5626</v>
       </c>
       <c r="I39" t="n">
         <v>2.5841</v>
@@ -2250,7 +2250,7 @@
         <v>0.8028</v>
       </c>
       <c r="D40" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="E40" t="n">
         <v>1.2741</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.2574</v>
+        <v>1.2527</v>
       </c>
       <c r="C41" t="n">
-        <v>0.7922</v>
+        <v>0.7893</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0866</v>
+        <v>0.0552</v>
       </c>
       <c r="E41" t="n">
-        <v>1.2574</v>
+        <v>1.2527</v>
       </c>
       <c r="F41" t="n">
-        <v>1.2574</v>
+        <v>1.2527</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.2574</v>
+        <v>1.2527</v>
       </c>
       <c r="I41" t="n">
         <v>1.2633</v>
@@ -2342,7 +2342,7 @@
         <v>0.7529</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0614</v>
+        <v>0.0321</v>
       </c>
       <c r="E42" t="n">
         <v>1.1949</v>
@@ -2388,7 +2388,7 @@
         <v>0.6445</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.0081</v>
+        <v>-0.0364</v>
       </c>
       <c r="E43" t="n">
         <v>1.0229</v>
@@ -2434,7 +2434,7 @@
         <v>0.3838</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.1753</v>
+        <v>-0.2012</v>
       </c>
       <c r="E44" t="n">
         <v>0.6092</v>
@@ -2480,7 +2480,7 @@
         <v>0.3291</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.2104</v>
+        <v>-0.2358</v>
       </c>
       <c r="E45" t="n">
         <v>0.5223</v>
@@ -2526,7 +2526,7 @@
         <v>0.3189</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2169</v>
+        <v>-0.2422</v>
       </c>
       <c r="E46" t="n">
         <v>0.5062</v>
@@ -2572,7 +2572,7 @@
         <v>0.1866</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3017</v>
+        <v>-0.3259</v>
       </c>
       <c r="E47" t="n">
         <v>0.2961</v>
@@ -2618,7 +2618,7 @@
         <v>0.1563</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3211</v>
+        <v>-0.3451</v>
       </c>
       <c r="E48" t="n">
         <v>0.2481</v>
@@ -2664,7 +2664,7 @@
         <v>0.1471</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.327</v>
+        <v>-0.3509</v>
       </c>
       <c r="E49" t="n">
         <v>0.2335</v>
@@ -2710,7 +2710,7 @@
         <v>0.138</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3329</v>
+        <v>-0.3566</v>
       </c>
       <c r="E50" t="n">
         <v>0.2191</v>
@@ -2756,7 +2756,7 @@
         <v>0.1217</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3433</v>
+        <v>-0.3669</v>
       </c>
       <c r="E51" t="n">
         <v>0.1932</v>
@@ -2802,7 +2802,7 @@
         <v>0.0516</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.3883</v>
+        <v>-0.4113</v>
       </c>
       <c r="E52" t="n">
         <v>0.0819</v>
@@ -2848,7 +2848,7 @@
         <v>0.018</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4098</v>
+        <v>-0.4326</v>
       </c>
       <c r="E53" t="n">
         <v>0.0285</v>
@@ -2894,7 +2894,7 @@
         <v>-0.09</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4791</v>
+        <v>-0.5008</v>
       </c>
       <c r="E54" t="n">
         <v>-0.1429</v>
@@ -2940,7 +2940,7 @@
         <v>-0.1368</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5091</v>
+        <v>-0.5304</v>
       </c>
       <c r="E55" t="n">
         <v>-0.2172</v>
@@ -2986,7 +2986,7 @@
         <v>-0.1499</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5175</v>
+        <v>-0.5387</v>
       </c>
       <c r="E56" t="n">
         <v>-0.2379</v>
@@ -3032,7 +3032,7 @@
         <v>-0.2274</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.5672</v>
+        <v>-0.5877</v>
       </c>
       <c r="E57" t="n">
         <v>-0.361</v>
@@ -3078,7 +3078,7 @@
         <v>-0.2516</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.5827</v>
+        <v>-0.603</v>
       </c>
       <c r="E58" t="n">
         <v>-0.3993</v>
@@ -3124,7 +3124,7 @@
         <v>-0.2694</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5941</v>
+        <v>-0.6143</v>
       </c>
       <c r="E59" t="n">
         <v>-0.4276</v>
@@ -3170,7 +3170,7 @@
         <v>-0.2937</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6097</v>
+        <v>-0.6296</v>
       </c>
       <c r="E60" t="n">
         <v>-0.4662</v>
@@ -3216,7 +3216,7 @@
         <v>-0.3842</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6677</v>
+        <v>-0.6869</v>
       </c>
       <c r="E61" t="n">
         <v>-0.6098</v>
@@ -3262,7 +3262,7 @@
         <v>-0.427</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6951000000000001</v>
+        <v>-0.7139</v>
       </c>
       <c r="E62" t="n">
         <v>-0.6777</v>
@@ -3308,7 +3308,7 @@
         <v>-0.4417</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7046</v>
+        <v>-0.7232</v>
       </c>
       <c r="E63" t="n">
         <v>-0.7010999999999999</v>
@@ -3354,7 +3354,7 @@
         <v>-0.6783</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.8562</v>
+        <v>-0.8728</v>
       </c>
       <c r="E64" t="n">
         <v>-1.0765</v>
@@ -3400,7 +3400,7 @@
         <v>-0.6866</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8616</v>
+        <v>-0.878</v>
       </c>
       <c r="E65" t="n">
         <v>-1.0897</v>
@@ -3446,7 +3446,7 @@
         <v>-0.8185</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.9462</v>
+        <v>-0.9615</v>
       </c>
       <c r="E66" t="n">
         <v>-1.2991</v>
@@ -3492,7 +3492,7 @@
         <v>-0.8194</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9467</v>
+        <v>-0.962</v>
       </c>
       <c r="E67" t="n">
         <v>-1.3005</v>
@@ -3538,7 +3538,7 @@
         <v>-0.9018</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9996</v>
+        <v>-1.0141</v>
       </c>
       <c r="E68" t="n">
         <v>-1.4313</v>
@@ -3584,7 +3584,7 @@
         <v>-0.9089</v>
       </c>
       <c r="D69" t="n">
-        <v>-1.0041</v>
+        <v>-1.0186</v>
       </c>
       <c r="E69" t="n">
         <v>-1.4426</v>
@@ -3630,7 +3630,7 @@
         <v>-0.9218</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.0124</v>
+        <v>-1.0268</v>
       </c>
       <c r="E70" t="n">
         <v>-1.463</v>
@@ -3676,7 +3676,7 @@
         <v>-0.9853</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.0531</v>
+        <v>-1.067</v>
       </c>
       <c r="E71" t="n">
         <v>-1.5639</v>
@@ -3722,7 +3722,7 @@
         <v>-1.0086</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.068</v>
+        <v>-1.0817</v>
       </c>
       <c r="E72" t="n">
         <v>-1.6008</v>
@@ -3768,7 +3768,7 @@
         <v>-1.0526</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.0963</v>
+        <v>-1.1095</v>
       </c>
       <c r="E73" t="n">
         <v>-1.6707</v>
@@ -3814,7 +3814,7 @@
         <v>-1.0688</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.1067</v>
+        <v>-1.1198</v>
       </c>
       <c r="E74" t="n">
         <v>-1.6964</v>
@@ -3860,7 +3860,7 @@
         <v>-1.2034</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.193</v>
+        <v>-1.2049</v>
       </c>
       <c r="E75" t="n">
         <v>-1.91</v>
@@ -3900,25 +3900,25 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.9648</v>
+        <v>-1.9509</v>
       </c>
       <c r="C76" t="n">
-        <v>-1.2379</v>
+        <v>-1.2292</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.2151</v>
+        <v>-1.2211</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.9648</v>
+        <v>-1.9509</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.8568</v>
+        <v>-1.8429</v>
       </c>
       <c r="G76" t="n">
         <v>-0.108</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.8568</v>
+        <v>-1.8429</v>
       </c>
       <c r="I76" t="n">
         <v>-1.8741</v>
@@ -3952,7 +3952,7 @@
         <v>-1.4748</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.367</v>
+        <v>-1.3764</v>
       </c>
       <c r="E77" t="n">
         <v>-2.3407</v>
@@ -3992,25 +3992,25 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-2.7187</v>
+        <v>-2.7086</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.7129</v>
+        <v>-1.7066</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.5197</v>
+        <v>-1.523</v>
       </c>
       <c r="E78" t="n">
-        <v>-2.7187</v>
+        <v>-2.7086</v>
       </c>
       <c r="F78" t="n">
-        <v>-2.7187</v>
+        <v>-2.7086</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-2.7187</v>
+        <v>-2.7086</v>
       </c>
       <c r="I78" t="n">
         <v>-2.7314</v>
@@ -4044,7 +4044,7 @@
         <v>-1.7665</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.554</v>
+        <v>-1.5609</v>
       </c>
       <c r="E79" t="n">
         <v>-2.8038</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-3.1937</v>
+        <v>-3.1841</v>
       </c>
       <c r="C80" t="n">
-        <v>-2.0122</v>
+        <v>-2.0062</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.7115</v>
+        <v>-1.7125</v>
       </c>
       <c r="E80" t="n">
-        <v>-3.1937</v>
+        <v>-3.1841</v>
       </c>
       <c r="F80" t="n">
-        <v>-1.283</v>
+        <v>-1.2734</v>
       </c>
       <c r="G80" t="n">
         <v>-1.9107</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.283</v>
+        <v>-1.2734</v>
       </c>
       <c r="I80" t="n">
         <v>-1.2949</v>
@@ -4136,7 +4136,7 @@
         <v>-2.1535</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.8021</v>
+        <v>-1.8056</v>
       </c>
       <c r="E81" t="n">
         <v>-3.4179</v>

--- a/database/event/8038/event_8038_evp_summary.xlsx
+++ b/database/event/8038/event_8038_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.9519</v>
+        <v>11.4052</v>
       </c>
       <c r="C2" t="n">
-        <v>6.9003</v>
+        <v>7.1859</v>
       </c>
       <c r="D2" t="n">
-        <v>4.3613</v>
+        <v>4.4806</v>
       </c>
       <c r="E2" t="n">
-        <v>10.9519</v>
+        <v>11.4052</v>
       </c>
       <c r="F2" t="n">
         <v>4.5807</v>
       </c>
       <c r="G2" t="n">
-        <v>6.3713</v>
+        <v>6.3718</v>
       </c>
       <c r="H2" t="n">
-        <v>12.9096</v>
+        <v>12.9098</v>
       </c>
       <c r="I2" t="n">
-        <v>6.9711</v>
+        <v>6.9712</v>
       </c>
       <c r="J2" t="n">
-        <v>6.3713</v>
+        <v>6.3718</v>
       </c>
       <c r="K2" t="n">
         <v>184</v>
@@ -529,7 +529,7 @@
         <v>128</v>
       </c>
       <c r="M2" t="n">
-        <v>13.3424</v>
+        <v>13.343</v>
       </c>
       <c r="N2" t="n">
         <v>312</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.8144</v>
+        <v>5.958</v>
       </c>
       <c r="C3" t="n">
-        <v>3.6634</v>
+        <v>3.7539</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0226</v>
+        <v>2.0475</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8144</v>
+        <v>5.958</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4276</v>
+        <v>2.4281</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3867</v>
+        <v>3.385</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5884</v>
+        <v>2.5895</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6551</v>
+        <v>2.6562</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3867</v>
+        <v>3.385</v>
       </c>
       <c r="K3" t="n">
         <v>177</v>
@@ -575,7 +575,7 @@
         <v>188</v>
       </c>
       <c r="M3" t="n">
-        <v>6.0418</v>
+        <v>6.0412</v>
       </c>
       <c r="N3" t="n">
         <v>365</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.6332</v>
+        <v>5.8387</v>
       </c>
       <c r="C4" t="n">
-        <v>3.5492</v>
+        <v>3.6787</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9401</v>
+        <v>1.9942</v>
       </c>
       <c r="E4" t="n">
-        <v>5.6332</v>
+        <v>5.8387</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2156</v>
+        <v>3.2158</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4176</v>
+        <v>2.4174</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3131</v>
+        <v>4.3133</v>
       </c>
       <c r="I4" t="n">
-        <v>4.5382</v>
+        <v>4.5385</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4176</v>
+        <v>2.4174</v>
       </c>
       <c r="K4" t="n">
         <v>212</v>
@@ -621,7 +621,7 @@
         <v>124</v>
       </c>
       <c r="M4" t="n">
-        <v>6.9558</v>
+        <v>6.9559</v>
       </c>
       <c r="N4" t="n">
         <v>336</v>
@@ -630,93 +630,93 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>iM</t>
+          <t>sh1ro</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.953</v>
+        <v>5.0918</v>
       </c>
       <c r="C5" t="n">
-        <v>3.1207</v>
+        <v>3.2081</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6305</v>
+        <v>1.6606</v>
       </c>
       <c r="E5" t="n">
-        <v>4.953</v>
+        <v>5.0918</v>
       </c>
       <c r="F5" t="n">
-        <v>4.0209</v>
+        <v>4.0089</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9321</v>
+        <v>0.8999</v>
       </c>
       <c r="H5" t="n">
-        <v>6.0754</v>
+        <v>8.332700000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>6.3926</v>
+        <v>4.4996</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9321</v>
+        <v>0.8999</v>
       </c>
       <c r="K5" t="n">
-        <v>212</v>
+        <v>184</v>
       </c>
       <c r="L5" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="M5" t="n">
-        <v>7.3247</v>
+        <v>5.3995</v>
       </c>
       <c r="N5" t="n">
-        <v>336</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sh1ro</t>
+          <t>iM</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.8947</v>
+        <v>5.0307</v>
       </c>
       <c r="C6" t="n">
-        <v>3.0839</v>
+        <v>3.1696</v>
       </c>
       <c r="D6" t="n">
-        <v>1.604</v>
+        <v>1.6333</v>
       </c>
       <c r="E6" t="n">
-        <v>4.8947</v>
+        <v>5.0307</v>
       </c>
       <c r="F6" t="n">
-        <v>4.0086</v>
+        <v>4.0209</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8861</v>
+        <v>0.9319</v>
       </c>
       <c r="H6" t="n">
-        <v>8.331799999999999</v>
+        <v>6.0756</v>
       </c>
       <c r="I6" t="n">
-        <v>4.4991</v>
+        <v>6.3928</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8861</v>
+        <v>0.9319</v>
       </c>
       <c r="K6" t="n">
-        <v>184</v>
+        <v>212</v>
       </c>
       <c r="L6" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="M6" t="n">
-        <v>5.3852</v>
+        <v>7.3247</v>
       </c>
       <c r="N6" t="n">
-        <v>312</v>
+        <v>336</v>
       </c>
     </row>
     <row r="7">
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.6424</v>
+        <v>4.6864</v>
       </c>
       <c r="C7" t="n">
-        <v>2.925</v>
+        <v>2.9527</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4891</v>
+        <v>1.4795</v>
       </c>
       <c r="E7" t="n">
-        <v>4.6424</v>
+        <v>4.6864</v>
       </c>
       <c r="F7" t="n">
-        <v>3.4258</v>
+        <v>3.4259</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2166</v>
+        <v>1.2466</v>
       </c>
       <c r="H7" t="n">
-        <v>4.773</v>
+        <v>4.7733</v>
       </c>
       <c r="I7" t="n">
-        <v>5.0222</v>
+        <v>5.0225</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2166</v>
+        <v>1.2466</v>
       </c>
       <c r="K7" t="n">
         <v>212</v>
@@ -759,7 +759,7 @@
         <v>124</v>
       </c>
       <c r="M7" t="n">
-        <v>6.238799999999999</v>
+        <v>6.2691</v>
       </c>
       <c r="N7" t="n">
         <v>336</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.5966</v>
+        <v>4.6475</v>
       </c>
       <c r="C8" t="n">
-        <v>2.8961</v>
+        <v>2.9282</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4683</v>
+        <v>1.4621</v>
       </c>
       <c r="E8" t="n">
-        <v>4.5966</v>
+        <v>4.6475</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2285</v>
+        <v>3.2286</v>
       </c>
       <c r="G8" t="n">
-        <v>1.3681</v>
+        <v>1.3674</v>
       </c>
       <c r="H8" t="n">
-        <v>5.7577</v>
+        <v>5.7581</v>
       </c>
       <c r="I8" t="n">
-        <v>3.1091</v>
+        <v>3.1093</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3681</v>
+        <v>1.3674</v>
       </c>
       <c r="K8" t="n">
         <v>125</v>
@@ -805,7 +805,7 @@
         <v>43</v>
       </c>
       <c r="M8" t="n">
-        <v>4.4772</v>
+        <v>4.4767</v>
       </c>
       <c r="N8" t="n">
         <v>168</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.1421</v>
+        <v>4.4363</v>
       </c>
       <c r="C9" t="n">
-        <v>2.6098</v>
+        <v>2.7951</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2614</v>
+        <v>1.3678</v>
       </c>
       <c r="E9" t="n">
-        <v>4.1421</v>
+        <v>4.4363</v>
       </c>
       <c r="F9" t="n">
-        <v>3.3494</v>
+        <v>3.3495</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7927</v>
+        <v>0.8034</v>
       </c>
       <c r="H9" t="n">
-        <v>4.6058</v>
+        <v>4.6061</v>
       </c>
       <c r="I9" t="n">
-        <v>4.8462</v>
+        <v>4.8465</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7927</v>
+        <v>0.8034</v>
       </c>
       <c r="K9" t="n">
         <v>191</v>
@@ -851,7 +851,7 @@
         <v>82</v>
       </c>
       <c r="M9" t="n">
-        <v>5.6389</v>
+        <v>5.6499</v>
       </c>
       <c r="N9" t="n">
         <v>273</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.0345</v>
+        <v>4.1645</v>
       </c>
       <c r="C10" t="n">
-        <v>2.542</v>
+        <v>2.6239</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2124</v>
+        <v>1.2464</v>
       </c>
       <c r="E10" t="n">
-        <v>4.0345</v>
+        <v>4.1645</v>
       </c>
       <c r="F10" t="n">
-        <v>3.9758</v>
+        <v>3.976</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0587</v>
+        <v>0.0581</v>
       </c>
       <c r="H10" t="n">
-        <v>8.2235</v>
+        <v>8.2242</v>
       </c>
       <c r="I10" t="n">
-        <v>4.4406</v>
+        <v>4.441</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0587</v>
+        <v>0.0581</v>
       </c>
       <c r="K10" t="n">
         <v>125</v>
@@ -897,7 +897,7 @@
         <v>43</v>
       </c>
       <c r="M10" t="n">
-        <v>4.4993</v>
+        <v>4.499099999999999</v>
       </c>
       <c r="N10" t="n">
         <v>168</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.8025</v>
+        <v>3.972</v>
       </c>
       <c r="C11" t="n">
-        <v>2.3958</v>
+        <v>2.5026</v>
       </c>
       <c r="D11" t="n">
-        <v>1.1068</v>
+        <v>1.1604</v>
       </c>
       <c r="E11" t="n">
-        <v>3.8025</v>
+        <v>3.972</v>
       </c>
       <c r="F11" t="n">
-        <v>3.8025</v>
+        <v>3.8026</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>5.5975</v>
+        <v>5.5977</v>
       </c>
       <c r="I11" t="n">
-        <v>5.7417</v>
+        <v>5.7419</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>5.7417</v>
+        <v>5.7419</v>
       </c>
       <c r="N11" t="n">
         <v>175</v>
@@ -952,139 +952,139 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>kyousuke</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.5452</v>
+        <v>3.8529</v>
       </c>
       <c r="C12" t="n">
-        <v>2.2337</v>
+        <v>2.4275</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9896</v>
+        <v>1.1072</v>
       </c>
       <c r="E12" t="n">
-        <v>3.5452</v>
+        <v>3.8529</v>
       </c>
       <c r="F12" t="n">
-        <v>3.5452</v>
+        <v>3.4509</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>5.0345</v>
+        <v>4.828</v>
       </c>
       <c r="I12" t="n">
-        <v>5.1642</v>
+        <v>4.828</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>5.1642</v>
+        <v>4.828</v>
       </c>
       <c r="N12" t="n">
-        <v>175</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.5241</v>
+        <v>3.6006</v>
       </c>
       <c r="C13" t="n">
-        <v>2.2204</v>
+        <v>2.2686</v>
       </c>
       <c r="D13" t="n">
-        <v>0.98</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>3.5241</v>
+        <v>3.6006</v>
       </c>
       <c r="F13" t="n">
-        <v>3.3765</v>
+        <v>3.5454</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1476</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>4.6652</v>
+        <v>5.0349</v>
       </c>
       <c r="I13" t="n">
-        <v>4.9087</v>
+        <v>5.1646</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1476</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="L13" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>5.056299999999999</v>
+        <v>5.1646</v>
       </c>
       <c r="N13" t="n">
-        <v>273</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kyousuke</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.4509</v>
+        <v>3.5654</v>
       </c>
       <c r="C14" t="n">
-        <v>2.1743</v>
+        <v>2.2464</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9467</v>
+        <v>0.9788</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4509</v>
+        <v>3.5654</v>
       </c>
       <c r="F14" t="n">
-        <v>3.4509</v>
+        <v>3.3708</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.1303</v>
       </c>
       <c r="H14" t="n">
-        <v>4.828</v>
+        <v>4.6527</v>
       </c>
       <c r="I14" t="n">
-        <v>4.828</v>
+        <v>4.8956</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.1303</v>
       </c>
       <c r="K14" t="n">
-        <v>151</v>
+        <v>191</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M14" t="n">
-        <v>4.828</v>
+        <v>5.0259</v>
       </c>
       <c r="N14" t="n">
-        <v>151</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15">
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.2105</v>
+        <v>3.2716</v>
       </c>
       <c r="C15" t="n">
-        <v>2.0228</v>
+        <v>2.0613</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8373</v>
+        <v>0.8475</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2105</v>
+        <v>3.2716</v>
       </c>
       <c r="F15" t="n">
-        <v>3.1514</v>
+        <v>3.1515</v>
       </c>
       <c r="G15" t="n">
         <v>0.0591</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1724</v>
+        <v>4.1727</v>
       </c>
       <c r="I15" t="n">
-        <v>4.3902</v>
+        <v>4.3905</v>
       </c>
       <c r="J15" t="n">
         <v>0.0591</v>
@@ -1127,7 +1127,7 @@
         <v>82</v>
       </c>
       <c r="M15" t="n">
-        <v>4.4493</v>
+        <v>4.4496</v>
       </c>
       <c r="N15" t="n">
         <v>273</v>
@@ -1136,93 +1136,93 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>xertioN</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.0995</v>
+        <v>3.22</v>
       </c>
       <c r="C16" t="n">
-        <v>1.9529</v>
+        <v>2.0288</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7868000000000001</v>
+        <v>0.8245</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0995</v>
+        <v>3.22</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5071</v>
+        <v>2.8914</v>
       </c>
       <c r="G16" t="n">
-        <v>1.5924</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5071</v>
+        <v>3.6034</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5459</v>
+        <v>3.6034</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5924</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>177</v>
+        <v>139</v>
       </c>
       <c r="L16" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.1383</v>
+        <v>3.6034</v>
       </c>
       <c r="N16" t="n">
-        <v>365</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>makazze</t>
+          <t>xertioN</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.0426</v>
+        <v>3.1786</v>
       </c>
       <c r="C17" t="n">
-        <v>1.917</v>
+        <v>2.0027</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7609</v>
+        <v>0.806</v>
       </c>
       <c r="E17" t="n">
-        <v>3.0426</v>
+        <v>3.1786</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7635999999999999</v>
+        <v>1.5077</v>
       </c>
       <c r="G17" t="n">
-        <v>2.279</v>
+        <v>1.5914</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7635999999999999</v>
+        <v>1.5077</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8035</v>
+        <v>1.5466</v>
       </c>
       <c r="J17" t="n">
-        <v>2.279</v>
+        <v>1.5914</v>
       </c>
       <c r="K17" t="n">
-        <v>212</v>
+        <v>177</v>
       </c>
       <c r="L17" t="n">
-        <v>124</v>
+        <v>188</v>
       </c>
       <c r="M17" t="n">
-        <v>3.0825</v>
+        <v>3.138</v>
       </c>
       <c r="N17" t="n">
-        <v>336</v>
+        <v>365</v>
       </c>
     </row>
     <row r="18">
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.0086</v>
+        <v>3.1562</v>
       </c>
       <c r="C18" t="n">
-        <v>1.8956</v>
+        <v>1.9886</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7454</v>
+        <v>0.796</v>
       </c>
       <c r="E18" t="n">
-        <v>3.0086</v>
+        <v>3.1562</v>
       </c>
       <c r="F18" t="n">
-        <v>3.0086</v>
+        <v>3.016</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>3.86</v>
+        <v>3.8762</v>
       </c>
       <c r="I18" t="n">
-        <v>3.86</v>
+        <v>3.8762</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.86</v>
+        <v>3.8762</v>
       </c>
       <c r="N18" t="n">
         <v>175</v>
@@ -1274,277 +1274,277 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>makazze</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.8922</v>
+        <v>3.0395</v>
       </c>
       <c r="C19" t="n">
-        <v>1.8222</v>
+        <v>1.9151</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6924</v>
+        <v>0.7439</v>
       </c>
       <c r="E19" t="n">
-        <v>2.8922</v>
+        <v>3.0395</v>
       </c>
       <c r="F19" t="n">
-        <v>2.8922</v>
+        <v>0.7638</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2.2785</v>
       </c>
       <c r="H19" t="n">
-        <v>3.6051</v>
+        <v>0.7638</v>
       </c>
       <c r="I19" t="n">
-        <v>3.6051</v>
+        <v>0.8037</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>2.2785</v>
       </c>
       <c r="K19" t="n">
-        <v>139</v>
+        <v>212</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6051</v>
+        <v>3.0822</v>
       </c>
       <c r="N19" t="n">
-        <v>139</v>
+        <v>336</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>zont1x</t>
+          <t>ZywOo</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.7902</v>
+        <v>2.815</v>
       </c>
       <c r="C20" t="n">
-        <v>1.758</v>
+        <v>1.7736</v>
       </c>
       <c r="D20" t="n">
-        <v>0.646</v>
+        <v>0.6435999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>2.7902</v>
+        <v>2.815</v>
       </c>
       <c r="F20" t="n">
-        <v>2.5547</v>
+        <v>3.593</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2355</v>
+        <v>-0.8084</v>
       </c>
       <c r="H20" t="n">
-        <v>3.5349</v>
+        <v>6.9605</v>
       </c>
       <c r="I20" t="n">
-        <v>1.9088</v>
+        <v>3.7586</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2355</v>
+        <v>-0.8084</v>
       </c>
       <c r="K20" t="n">
-        <v>184</v>
+        <v>125</v>
       </c>
       <c r="L20" t="n">
-        <v>128</v>
+        <v>43</v>
       </c>
       <c r="M20" t="n">
-        <v>2.1443</v>
+        <v>2.9502</v>
       </c>
       <c r="N20" t="n">
-        <v>312</v>
+        <v>168</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ZywOo</t>
+          <t>ewjerkz</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.7845</v>
+        <v>2.7973</v>
       </c>
       <c r="C21" t="n">
-        <v>1.7544</v>
+        <v>1.7625</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6434</v>
+        <v>0.6357</v>
       </c>
       <c r="E21" t="n">
-        <v>2.7845</v>
+        <v>2.7973</v>
       </c>
       <c r="F21" t="n">
-        <v>3.5928</v>
+        <v>2.6599</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8083</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>6.9599</v>
+        <v>3.0967</v>
       </c>
       <c r="I21" t="n">
-        <v>3.7583</v>
+        <v>3.0967</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8083</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="L21" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.95</v>
+        <v>3.0967</v>
       </c>
       <c r="N21" t="n">
-        <v>168</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.7157</v>
+        <v>2.7702</v>
       </c>
       <c r="C22" t="n">
-        <v>1.711</v>
+        <v>1.7454</v>
       </c>
       <c r="D22" t="n">
-        <v>0.612</v>
+        <v>0.6236</v>
       </c>
       <c r="E22" t="n">
-        <v>2.7157</v>
+        <v>2.7702</v>
       </c>
       <c r="F22" t="n">
-        <v>3.108</v>
+        <v>2.7061</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3923</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>4.0775</v>
+        <v>3.1978</v>
       </c>
       <c r="I22" t="n">
-        <v>4.2904</v>
+        <v>3.2802</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3923</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="L22" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.8981</v>
+        <v>3.2802</v>
       </c>
       <c r="N22" t="n">
-        <v>273</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>zont1x</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.7059</v>
+        <v>2.6369</v>
       </c>
       <c r="C23" t="n">
-        <v>1.7049</v>
+        <v>1.6614</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6076</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>2.7059</v>
+        <v>2.6369</v>
       </c>
       <c r="F23" t="n">
-        <v>2.7059</v>
+        <v>2.547</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.2356</v>
       </c>
       <c r="H23" t="n">
-        <v>3.1975</v>
+        <v>3.5093</v>
       </c>
       <c r="I23" t="n">
-        <v>3.2799</v>
+        <v>1.895</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.2356</v>
       </c>
       <c r="K23" t="n">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2799</v>
+        <v>2.1306</v>
       </c>
       <c r="N23" t="n">
-        <v>175</v>
+        <v>312</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ewjerkz</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.6653</v>
+        <v>2.6324</v>
       </c>
       <c r="C24" t="n">
-        <v>1.6793</v>
+        <v>1.6586</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5891</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>2.6653</v>
+        <v>2.6324</v>
       </c>
       <c r="F24" t="n">
-        <v>2.6653</v>
+        <v>3.1083</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-0.3923</v>
       </c>
       <c r="H24" t="n">
-        <v>3.1085</v>
+        <v>4.0781</v>
       </c>
       <c r="I24" t="n">
-        <v>3.1085</v>
+        <v>4.291</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-0.3923</v>
       </c>
       <c r="K24" t="n">
-        <v>156</v>
+        <v>191</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M24" t="n">
-        <v>3.1085</v>
+        <v>3.8987</v>
       </c>
       <c r="N24" t="n">
-        <v>156</v>
+        <v>273</v>
       </c>
     </row>
     <row r="25">
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.6042</v>
+        <v>2.6198</v>
       </c>
       <c r="C25" t="n">
-        <v>1.6408</v>
+        <v>1.6506</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5613</v>
+        <v>0.5564</v>
       </c>
       <c r="E25" t="n">
-        <v>2.6042</v>
+        <v>2.6198</v>
       </c>
       <c r="F25" t="n">
-        <v>1.3215</v>
+        <v>1.3221</v>
       </c>
       <c r="G25" t="n">
-        <v>1.2827</v>
+        <v>1.3318</v>
       </c>
       <c r="H25" t="n">
-        <v>1.3215</v>
+        <v>1.3221</v>
       </c>
       <c r="I25" t="n">
-        <v>1.3556</v>
+        <v>1.3562</v>
       </c>
       <c r="J25" t="n">
-        <v>1.2827</v>
+        <v>1.3318</v>
       </c>
       <c r="K25" t="n">
         <v>177</v>
@@ -1587,7 +1587,7 @@
         <v>188</v>
       </c>
       <c r="M25" t="n">
-        <v>2.6383</v>
+        <v>2.688</v>
       </c>
       <c r="N25" t="n">
         <v>365</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.4167</v>
+        <v>2.4746</v>
       </c>
       <c r="C26" t="n">
-        <v>1.5227</v>
+        <v>1.5591</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4759</v>
+        <v>0.4915</v>
       </c>
       <c r="E26" t="n">
-        <v>2.4167</v>
+        <v>2.4746</v>
       </c>
       <c r="F26" t="n">
-        <v>2.9149</v>
+        <v>2.897</v>
       </c>
       <c r="G26" t="n">
         <v>-0.4982</v>
       </c>
       <c r="H26" t="n">
-        <v>3.6549</v>
+        <v>3.6156</v>
       </c>
       <c r="I26" t="n">
-        <v>3.6549</v>
+        <v>3.6156</v>
       </c>
       <c r="J26" t="n">
         <v>-0.4982</v>
@@ -1633,7 +1633,7 @@
         <v>59</v>
       </c>
       <c r="M26" t="n">
-        <v>3.1567</v>
+        <v>3.1174</v>
       </c>
       <c r="N26" t="n">
         <v>180</v>
@@ -1642,124 +1642,124 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>flameZ</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.3998</v>
+        <v>2.4625</v>
       </c>
       <c r="C27" t="n">
-        <v>1.512</v>
+        <v>1.5515</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4682</v>
+        <v>0.4861</v>
       </c>
       <c r="E27" t="n">
-        <v>2.3998</v>
+        <v>2.4625</v>
       </c>
       <c r="F27" t="n">
-        <v>3.2923</v>
+        <v>1.8777</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.8925</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>5.9684</v>
+        <v>1.8777</v>
       </c>
       <c r="I27" t="n">
-        <v>3.2229</v>
+        <v>1.8777</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.8925</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>125</v>
+        <v>76</v>
       </c>
       <c r="L27" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2.3304</v>
+        <v>1.8777</v>
       </c>
       <c r="N27" t="n">
-        <v>168</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>flameZ</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.3128</v>
+        <v>2.3934</v>
       </c>
       <c r="C28" t="n">
-        <v>1.4572</v>
+        <v>1.508</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4286</v>
+        <v>0.4553</v>
       </c>
       <c r="E28" t="n">
-        <v>2.3128</v>
+        <v>2.3934</v>
       </c>
       <c r="F28" t="n">
-        <v>2.3128</v>
+        <v>3.2814</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-0.8829</v>
       </c>
       <c r="H28" t="n">
-        <v>2.337</v>
+        <v>5.9323</v>
       </c>
       <c r="I28" t="n">
-        <v>2.337</v>
+        <v>3.2034</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-0.8829</v>
       </c>
       <c r="K28" t="n">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M28" t="n">
-        <v>2.337</v>
+        <v>2.3205</v>
       </c>
       <c r="N28" t="n">
-        <v>151</v>
+        <v>168</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.2243</v>
+        <v>2.3262</v>
       </c>
       <c r="C29" t="n">
-        <v>1.4014</v>
+        <v>1.4656</v>
       </c>
       <c r="D29" t="n">
-        <v>0.3883</v>
+        <v>0.4252</v>
       </c>
       <c r="E29" t="n">
-        <v>2.2243</v>
+        <v>2.3262</v>
       </c>
       <c r="F29" t="n">
-        <v>2.2243</v>
+        <v>2.1973</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2.2243</v>
+        <v>2.1973</v>
       </c>
       <c r="I29" t="n">
-        <v>2.2243</v>
+        <v>2.2539</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>2.2243</v>
+        <v>2.2539</v>
       </c>
       <c r="N29" t="n">
         <v>175</v>
@@ -1780,47 +1780,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.2083</v>
+        <v>2.3153</v>
       </c>
       <c r="C30" t="n">
-        <v>1.3914</v>
+        <v>1.4588</v>
       </c>
       <c r="D30" t="n">
-        <v>0.3811</v>
+        <v>0.4204</v>
       </c>
       <c r="E30" t="n">
-        <v>2.2083</v>
+        <v>2.3153</v>
       </c>
       <c r="F30" t="n">
-        <v>2.2083</v>
+        <v>2.3128</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>2.2083</v>
+        <v>2.337</v>
       </c>
       <c r="I30" t="n">
-        <v>2.2652</v>
+        <v>2.337</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>2.2652</v>
+        <v>2.337</v>
       </c>
       <c r="N30" t="n">
-        <v>175</v>
+        <v>151</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.1324</v>
+        <v>2.3094</v>
       </c>
       <c r="C31" t="n">
-        <v>1.3435</v>
+        <v>1.455</v>
       </c>
       <c r="D31" t="n">
-        <v>0.3465</v>
+        <v>0.4177</v>
       </c>
       <c r="E31" t="n">
-        <v>2.1324</v>
+        <v>2.3094</v>
       </c>
       <c r="F31" t="n">
-        <v>2.1324</v>
+        <v>2.1811</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2.1324</v>
+        <v>2.1811</v>
       </c>
       <c r="I31" t="n">
-        <v>2.1324</v>
+        <v>2.1811</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>2.1324</v>
+        <v>2.1811</v>
       </c>
       <c r="N31" t="n">
         <v>163</v>
@@ -1872,170 +1872,170 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.0358</v>
+        <v>2.1827</v>
       </c>
       <c r="C32" t="n">
-        <v>1.2827</v>
+        <v>1.3752</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3025</v>
+        <v>0.3611</v>
       </c>
       <c r="E32" t="n">
-        <v>2.0358</v>
+        <v>2.1827</v>
       </c>
       <c r="F32" t="n">
-        <v>1.4949</v>
+        <v>2.2241</v>
       </c>
       <c r="G32" t="n">
-        <v>0.5409</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>1.4949</v>
+        <v>2.2241</v>
       </c>
       <c r="I32" t="n">
-        <v>1.4949</v>
+        <v>2.2241</v>
       </c>
       <c r="J32" t="n">
-        <v>0.5409</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>121</v>
+        <v>175</v>
       </c>
       <c r="L32" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>2.0358</v>
+        <v>2.2241</v>
       </c>
       <c r="N32" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Spinx</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.0173</v>
+        <v>2.164</v>
       </c>
       <c r="C33" t="n">
-        <v>1.271</v>
+        <v>1.3634</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2941</v>
+        <v>0.3528</v>
       </c>
       <c r="E33" t="n">
-        <v>2.0173</v>
+        <v>2.164</v>
       </c>
       <c r="F33" t="n">
-        <v>0.6437</v>
+        <v>1.4954</v>
       </c>
       <c r="G33" t="n">
-        <v>1.3736</v>
+        <v>0.5409</v>
       </c>
       <c r="H33" t="n">
-        <v>0.6437</v>
+        <v>1.4954</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6603</v>
+        <v>1.4954</v>
       </c>
       <c r="J33" t="n">
-        <v>1.3736</v>
+        <v>0.5409</v>
       </c>
       <c r="K33" t="n">
-        <v>177</v>
+        <v>121</v>
       </c>
       <c r="L33" t="n">
-        <v>188</v>
+        <v>59</v>
       </c>
       <c r="M33" t="n">
-        <v>2.0339</v>
+        <v>2.0363</v>
       </c>
       <c r="N33" t="n">
-        <v>365</v>
+        <v>180</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MATYS</t>
+          <t>Spinx</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.9297</v>
+        <v>2.0882</v>
       </c>
       <c r="C34" t="n">
-        <v>1.2158</v>
+        <v>1.3157</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2542</v>
+        <v>0.3189</v>
       </c>
       <c r="E34" t="n">
-        <v>1.9297</v>
+        <v>2.0882</v>
       </c>
       <c r="F34" t="n">
-        <v>1.9297</v>
+        <v>0.6609</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1.3726</v>
       </c>
       <c r="H34" t="n">
-        <v>1.9297</v>
+        <v>0.6609</v>
       </c>
       <c r="I34" t="n">
-        <v>1.9297</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1.3726</v>
       </c>
       <c r="K34" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="M34" t="n">
-        <v>1.9297</v>
+        <v>2.0505</v>
       </c>
       <c r="N34" t="n">
-        <v>175</v>
+        <v>365</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.8924</v>
+        <v>2.0085</v>
       </c>
       <c r="C35" t="n">
-        <v>1.1923</v>
+        <v>1.2655</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2373</v>
+        <v>0.2833</v>
       </c>
       <c r="E35" t="n">
-        <v>1.8924</v>
+        <v>2.0085</v>
       </c>
       <c r="F35" t="n">
-        <v>1.8924</v>
+        <v>1.8974</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.8924</v>
+        <v>1.8974</v>
       </c>
       <c r="I35" t="n">
-        <v>1.8924</v>
+        <v>1.8974</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.8924</v>
+        <v>1.8974</v>
       </c>
       <c r="N35" t="n">
         <v>128</v>
@@ -2056,216 +2056,216 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Techno</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.8868</v>
+        <v>1.994</v>
       </c>
       <c r="C36" t="n">
-        <v>1.1888</v>
+        <v>1.2563</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2347</v>
+        <v>0.2769</v>
       </c>
       <c r="E36" t="n">
-        <v>1.8868</v>
+        <v>1.994</v>
       </c>
       <c r="F36" t="n">
-        <v>1.3511</v>
+        <v>1.8922</v>
       </c>
       <c r="G36" t="n">
-        <v>0.5357</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.3511</v>
+        <v>1.8922</v>
       </c>
       <c r="I36" t="n">
-        <v>1.3511</v>
+        <v>1.8922</v>
       </c>
       <c r="J36" t="n">
-        <v>0.5357</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="L36" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.8868</v>
+        <v>1.8922</v>
       </c>
       <c r="N36" t="n">
-        <v>180</v>
+        <v>128</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>Techno</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.8813</v>
+        <v>1.9398</v>
       </c>
       <c r="C37" t="n">
-        <v>1.1853</v>
+        <v>1.2222</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2322</v>
+        <v>0.2526</v>
       </c>
       <c r="E37" t="n">
-        <v>1.8813</v>
+        <v>1.9398</v>
       </c>
       <c r="F37" t="n">
-        <v>1.8813</v>
+        <v>1.3516</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>0.5357</v>
       </c>
       <c r="H37" t="n">
-        <v>1.8813</v>
+        <v>1.3516</v>
       </c>
       <c r="I37" t="n">
-        <v>1.8813</v>
+        <v>1.3516</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>0.5357</v>
       </c>
       <c r="K37" t="n">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M37" t="n">
-        <v>1.8813</v>
+        <v>1.8873</v>
       </c>
       <c r="N37" t="n">
-        <v>128</v>
+        <v>180</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>MATYS</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.8786</v>
+        <v>1.9208</v>
       </c>
       <c r="C38" t="n">
-        <v>1.1836</v>
+        <v>1.2102</v>
       </c>
       <c r="D38" t="n">
-        <v>0.231</v>
+        <v>0.2442</v>
       </c>
       <c r="E38" t="n">
-        <v>1.8786</v>
+        <v>1.9208</v>
       </c>
       <c r="F38" t="n">
-        <v>1.8786</v>
+        <v>1.9286</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.8786</v>
+        <v>1.9286</v>
       </c>
       <c r="I38" t="n">
-        <v>1.8786</v>
+        <v>1.9286</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>76</v>
+        <v>175</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1.8786</v>
+        <v>1.9286</v>
       </c>
       <c r="N38" t="n">
-        <v>76</v>
+        <v>175</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HeavyGod</t>
+          <t>xKacpersky</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.8138</v>
+        <v>1.8899</v>
       </c>
       <c r="C39" t="n">
-        <v>1.1428</v>
+        <v>1.1907</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2015</v>
+        <v>0.2304</v>
       </c>
       <c r="E39" t="n">
-        <v>1.8138</v>
+        <v>1.8899</v>
       </c>
       <c r="F39" t="n">
-        <v>1.8138</v>
+        <v>1.7885</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.8138</v>
+        <v>1.7885</v>
       </c>
       <c r="I39" t="n">
-        <v>1.8138</v>
+        <v>1.7885</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1.8138</v>
+        <v>1.7885</v>
       </c>
       <c r="N39" t="n">
-        <v>175</v>
+        <v>156</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>xKacpersky</t>
+          <t>r1nkle</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.7882</v>
+        <v>1.7727</v>
       </c>
       <c r="C40" t="n">
-        <v>1.1267</v>
+        <v>1.1169</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1898</v>
+        <v>0.178</v>
       </c>
       <c r="E40" t="n">
-        <v>1.7882</v>
+        <v>1.7727</v>
       </c>
       <c r="F40" t="n">
-        <v>1.7882</v>
+        <v>1.7637</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.7882</v>
+        <v>1.7637</v>
       </c>
       <c r="I40" t="n">
-        <v>1.7882</v>
+        <v>1.7637</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.7882</v>
+        <v>1.7637</v>
       </c>
       <c r="N40" t="n">
         <v>156</v>
@@ -2286,277 +2286,277 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>r1nkle</t>
+          <t>HeavyGod</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.7634</v>
+        <v>1.7198</v>
       </c>
       <c r="C41" t="n">
-        <v>1.111</v>
+        <v>1.0836</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1785</v>
+        <v>0.1544</v>
       </c>
       <c r="E41" t="n">
-        <v>1.7634</v>
+        <v>1.7198</v>
       </c>
       <c r="F41" t="n">
-        <v>1.7634</v>
+        <v>1.8371</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.7634</v>
+        <v>1.8371</v>
       </c>
       <c r="I41" t="n">
-        <v>1.7634</v>
+        <v>1.8371</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1.7634</v>
+        <v>1.8371</v>
       </c>
       <c r="N41" t="n">
-        <v>156</v>
+        <v>175</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Jimpphat</t>
+          <t>tN1R</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.5674</v>
+        <v>1.5213</v>
       </c>
       <c r="C42" t="n">
-        <v>0.9875</v>
+        <v>0.9585</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0893</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>1.5674</v>
+        <v>1.5213</v>
       </c>
       <c r="F42" t="n">
-        <v>2.4286</v>
+        <v>1.2961</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.8612</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>2.5905</v>
+        <v>1.2961</v>
       </c>
       <c r="I42" t="n">
-        <v>2.6573</v>
+        <v>1.2961</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.8612</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>177</v>
+        <v>87</v>
       </c>
       <c r="L42" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1.7961</v>
+        <v>1.2961</v>
       </c>
       <c r="N42" t="n">
-        <v>365</v>
+        <v>87</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>tN1R</t>
+          <t>ultimate</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.2967</v>
+        <v>1.4493</v>
       </c>
       <c r="C43" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.9131</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.0339</v>
+        <v>0.0336</v>
       </c>
       <c r="E43" t="n">
-        <v>1.2967</v>
+        <v>1.4493</v>
       </c>
       <c r="F43" t="n">
-        <v>1.2967</v>
+        <v>1.212</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1.2967</v>
+        <v>1.212</v>
       </c>
       <c r="I43" t="n">
-        <v>1.2967</v>
+        <v>1.212</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1.2967</v>
+        <v>1.212</v>
       </c>
       <c r="N43" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ultimate</t>
+          <t>Jimpphat</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.2032</v>
+        <v>1.4037</v>
       </c>
       <c r="C44" t="n">
-        <v>0.7581</v>
+        <v>0.8844</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.0765</v>
+        <v>0.0132</v>
       </c>
       <c r="E44" t="n">
-        <v>1.2032</v>
+        <v>1.4037</v>
       </c>
       <c r="F44" t="n">
-        <v>1.2032</v>
+        <v>2.4134</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>-0.8409</v>
       </c>
       <c r="H44" t="n">
-        <v>1.2032</v>
+        <v>2.5573</v>
       </c>
       <c r="I44" t="n">
-        <v>1.2032</v>
+        <v>2.6232</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>-0.8409</v>
       </c>
       <c r="K44" t="n">
-        <v>76</v>
+        <v>177</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>188</v>
       </c>
       <c r="M44" t="n">
-        <v>1.2032</v>
+        <v>1.7823</v>
       </c>
       <c r="N44" t="n">
-        <v>76</v>
+        <v>365</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.9725</v>
+        <v>1.016</v>
       </c>
       <c r="C45" t="n">
-        <v>0.6127</v>
+        <v>0.6401</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.1815</v>
+        <v>-0.16</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9725</v>
+        <v>1.016</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9725</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.9725</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>0.9725</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.9725</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="N45" t="n">
-        <v>151</v>
+        <v>139</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>yxngstxr</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8955</v>
+        <v>0.9833</v>
       </c>
       <c r="C46" t="n">
-        <v>0.5642</v>
+        <v>0.6195000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.2166</v>
+        <v>-0.1746</v>
       </c>
       <c r="E46" t="n">
-        <v>0.8955</v>
+        <v>0.9833</v>
       </c>
       <c r="F46" t="n">
-        <v>0.8955</v>
+        <v>0.7055</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.8955</v>
+        <v>0.7055</v>
       </c>
       <c r="I46" t="n">
-        <v>0.8955</v>
+        <v>0.7055</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>139</v>
+        <v>87</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.8955</v>
+        <v>0.7055</v>
       </c>
       <c r="N46" t="n">
-        <v>139</v>
+        <v>87</v>
       </c>
     </row>
     <row r="47">
@@ -2566,28 +2566,28 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7834</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="C47" t="n">
-        <v>0.4936</v>
+        <v>0.5351</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.2676</v>
+        <v>-0.2345</v>
       </c>
       <c r="E47" t="n">
-        <v>0.7834</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7834</v>
+        <v>0.7837</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.7834</v>
+        <v>0.7837</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7834</v>
+        <v>0.7837</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.7834</v>
+        <v>0.7837</v>
       </c>
       <c r="N47" t="n">
         <v>156</v>
@@ -2608,93 +2608,93 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>yxngstxr</t>
+          <t>jottAAA</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7057</v>
+        <v>0.7719</v>
       </c>
       <c r="C48" t="n">
-        <v>0.4446</v>
+        <v>0.4863</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.303</v>
+        <v>-0.269</v>
       </c>
       <c r="E48" t="n">
-        <v>0.7057</v>
+        <v>0.7719</v>
       </c>
       <c r="F48" t="n">
-        <v>0.7057</v>
+        <v>0.725</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0.7057</v>
+        <v>0.725</v>
       </c>
       <c r="I48" t="n">
-        <v>0.7057</v>
+        <v>0.725</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>87</v>
+        <v>139</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.7057</v>
+        <v>0.725</v>
       </c>
       <c r="N48" t="n">
-        <v>87</v>
+        <v>139</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>jottAAA</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6812</v>
+        <v>0.7526</v>
       </c>
       <c r="C49" t="n">
-        <v>0.4292</v>
+        <v>0.4742</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3141</v>
+        <v>-0.2777</v>
       </c>
       <c r="E49" t="n">
-        <v>0.6812</v>
+        <v>0.7526</v>
       </c>
       <c r="F49" t="n">
-        <v>0.6812</v>
+        <v>0.9725</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.6812</v>
+        <v>0.9725</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6812</v>
+        <v>0.9725</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.6812</v>
+        <v>0.9725</v>
       </c>
       <c r="N49" t="n">
-        <v>139</v>
+        <v>151</v>
       </c>
     </row>
     <row r="50">
@@ -2704,16 +2704,16 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6563</v>
+        <v>0.7524</v>
       </c>
       <c r="C50" t="n">
-        <v>0.4135</v>
+        <v>0.4741</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3254</v>
+        <v>-0.2777</v>
       </c>
       <c r="E50" t="n">
-        <v>0.6563</v>
+        <v>0.7524</v>
       </c>
       <c r="F50" t="n">
         <v>0.6563</v>
@@ -2746,173 +2746,173 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>mzinho</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6536</v>
+        <v>0.6394</v>
       </c>
       <c r="C51" t="n">
-        <v>0.4118</v>
+        <v>0.4029</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3267</v>
+        <v>-0.3282</v>
       </c>
       <c r="E51" t="n">
-        <v>0.6536</v>
+        <v>0.6394</v>
       </c>
       <c r="F51" t="n">
-        <v>1.4647</v>
+        <v>0.6345</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.8111</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>1.4647</v>
+        <v>0.6345</v>
       </c>
       <c r="I51" t="n">
-        <v>1.4647</v>
+        <v>0.6345</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.8111</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>121</v>
+        <v>163</v>
       </c>
       <c r="L51" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.6535999999999998</v>
+        <v>0.6345</v>
       </c>
       <c r="N51" t="n">
-        <v>180</v>
+        <v>163</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>Tauson</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6247</v>
+        <v>0.5</v>
       </c>
       <c r="C52" t="n">
-        <v>0.3936</v>
+        <v>0.315</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.3398</v>
+        <v>-0.3905</v>
       </c>
       <c r="E52" t="n">
-        <v>0.6247</v>
+        <v>0.5</v>
       </c>
       <c r="F52" t="n">
-        <v>0.6247</v>
+        <v>0.5656</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.6247</v>
+        <v>0.5656</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6247</v>
+        <v>0.5656</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.6247</v>
+        <v>0.5656</v>
       </c>
       <c r="N52" t="n">
-        <v>163</v>
+        <v>128</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Tauson</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5659</v>
+        <v>0.4983</v>
       </c>
       <c r="C53" t="n">
-        <v>0.3565</v>
+        <v>0.314</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.3666</v>
+        <v>-0.3912</v>
       </c>
       <c r="E53" t="n">
-        <v>0.5659</v>
+        <v>0.4983</v>
       </c>
       <c r="F53" t="n">
-        <v>0.5659</v>
+        <v>0.7365</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>-0.26</v>
       </c>
       <c r="H53" t="n">
-        <v>0.5659</v>
+        <v>0.7365</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5659</v>
+        <v>0.7365</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>-0.26</v>
       </c>
       <c r="K53" t="n">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M53" t="n">
-        <v>0.5659</v>
+        <v>0.4765</v>
       </c>
       <c r="N53" t="n">
-        <v>128</v>
+        <v>180</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>mzinho</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.476</v>
+        <v>0.4614</v>
       </c>
       <c r="C54" t="n">
-        <v>0.2999</v>
+        <v>0.2907</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.4075</v>
+        <v>-0.4077</v>
       </c>
       <c r="E54" t="n">
-        <v>0.476</v>
+        <v>0.4614</v>
       </c>
       <c r="F54" t="n">
-        <v>0.736</v>
+        <v>1.4753</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.26</v>
+        <v>-0.8111</v>
       </c>
       <c r="H54" t="n">
-        <v>0.736</v>
+        <v>1.4753</v>
       </c>
       <c r="I54" t="n">
-        <v>0.736</v>
+        <v>1.4753</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.26</v>
+        <v>-0.8111</v>
       </c>
       <c r="K54" t="n">
         <v>121</v>
@@ -2921,7 +2921,7 @@
         <v>59</v>
       </c>
       <c r="M54" t="n">
-        <v>0.476</v>
+        <v>0.6642</v>
       </c>
       <c r="N54" t="n">
         <v>180</v>
@@ -2934,31 +2934,31 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.3931</v>
+        <v>0.2546</v>
       </c>
       <c r="C55" t="n">
-        <v>0.2477</v>
+        <v>0.1604</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.4453</v>
+        <v>-0.5001</v>
       </c>
       <c r="E55" t="n">
-        <v>0.3931</v>
+        <v>0.2546</v>
       </c>
       <c r="F55" t="n">
-        <v>0.3552</v>
+        <v>0.3557</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0379</v>
+        <v>0.0377</v>
       </c>
       <c r="H55" t="n">
-        <v>0.3552</v>
+        <v>0.3557</v>
       </c>
       <c r="I55" t="n">
-        <v>0.1918</v>
+        <v>0.1921</v>
       </c>
       <c r="J55" t="n">
-        <v>0.0379</v>
+        <v>0.0377</v>
       </c>
       <c r="K55" t="n">
         <v>125</v>
@@ -2967,7 +2967,7 @@
         <v>43</v>
       </c>
       <c r="M55" t="n">
-        <v>0.2297</v>
+        <v>0.2298</v>
       </c>
       <c r="N55" t="n">
         <v>168</v>
@@ -2976,139 +2976,139 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.3597</v>
+        <v>0.2479</v>
       </c>
       <c r="C56" t="n">
-        <v>0.2266</v>
+        <v>0.1562</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.4605</v>
+        <v>-0.5031</v>
       </c>
       <c r="E56" t="n">
-        <v>0.3597</v>
+        <v>0.2479</v>
       </c>
       <c r="F56" t="n">
-        <v>0.3597</v>
+        <v>0.2772</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.3597</v>
+        <v>0.2772</v>
       </c>
       <c r="I56" t="n">
-        <v>0.3597</v>
+        <v>0.2772</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.3597</v>
+        <v>0.2772</v>
       </c>
       <c r="N56" t="n">
-        <v>151</v>
+        <v>163</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.312</v>
+        <v>0.217</v>
       </c>
       <c r="C57" t="n">
-        <v>0.1966</v>
+        <v>0.1367</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.4822</v>
+        <v>-0.5169</v>
       </c>
       <c r="E57" t="n">
-        <v>0.312</v>
+        <v>0.217</v>
       </c>
       <c r="F57" t="n">
-        <v>0.312</v>
+        <v>0.3597</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.312</v>
+        <v>0.3597</v>
       </c>
       <c r="I57" t="n">
-        <v>0.312</v>
+        <v>0.3597</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.312</v>
+        <v>0.3597</v>
       </c>
       <c r="N57" t="n">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.2791</v>
+        <v>0.1442</v>
       </c>
       <c r="C58" t="n">
-        <v>0.1758</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.4972</v>
+        <v>-0.5494</v>
       </c>
       <c r="E58" t="n">
-        <v>0.2791</v>
+        <v>0.1442</v>
       </c>
       <c r="F58" t="n">
-        <v>0.2791</v>
+        <v>0.3122</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.2791</v>
+        <v>0.3122</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2791</v>
+        <v>0.3122</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.2791</v>
+        <v>0.3122</v>
       </c>
       <c r="N58" t="n">
-        <v>163</v>
+        <v>156</v>
       </c>
     </row>
     <row r="59">
@@ -3118,16 +3118,16 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.1684</v>
+        <v>0.0556</v>
       </c>
       <c r="C59" t="n">
-        <v>0.1061</v>
+        <v>0.035</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5475</v>
+        <v>-0.589</v>
       </c>
       <c r="E59" t="n">
-        <v>0.1684</v>
+        <v>0.0556</v>
       </c>
       <c r="F59" t="n">
         <v>0.1684</v>
@@ -3164,16 +3164,16 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.0638</v>
+        <v>-0.0191</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.0402</v>
+        <v>-0.012</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6532</v>
+        <v>-0.6224</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.0638</v>
+        <v>-0.0191</v>
       </c>
       <c r="F60" t="n">
         <v>-0.0638</v>
@@ -3206,139 +3206,139 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>xfl0ud</t>
+          <t>Kursy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.2695</v>
+        <v>-0.2093</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.1698</v>
+        <v>-0.1319</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7469</v>
+        <v>-0.7073</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.2695</v>
+        <v>-0.2093</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.2695</v>
+        <v>-0.2794</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.2695</v>
+        <v>-0.2794</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2695</v>
+        <v>-0.2794</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.2695</v>
+        <v>-0.2794</v>
       </c>
       <c r="N61" t="n">
-        <v>139</v>
+        <v>128</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>xfl0ud</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.272</v>
+        <v>-0.352</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.1714</v>
+        <v>-0.2218</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.748</v>
+        <v>-0.7711</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.272</v>
+        <v>-0.352</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.272</v>
+        <v>-0.2612</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.272</v>
+        <v>-0.2612</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.272</v>
+        <v>-0.2612</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.272</v>
+        <v>-0.2612</v>
       </c>
       <c r="N62" t="n">
-        <v>163</v>
+        <v>139</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Kursy</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.2792</v>
+        <v>-0.3588</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.1759</v>
+        <v>-0.2261</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7513</v>
+        <v>-0.7741</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.2792</v>
+        <v>-0.3588</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.2792</v>
+        <v>-0.2608</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.2792</v>
+        <v>-0.2608</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.2792</v>
+        <v>-0.2608</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>128</v>
+        <v>163</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.2792</v>
+        <v>-0.2608</v>
       </c>
       <c r="N63" t="n">
-        <v>128</v>
+        <v>163</v>
       </c>
     </row>
     <row r="64">
@@ -3348,28 +3348,28 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.6371</v>
+        <v>-0.7317</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.4014</v>
+        <v>-0.461</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.9142</v>
+        <v>-0.9407</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.6371</v>
+        <v>-0.7317</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.6371</v>
+        <v>-0.6178</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.6371</v>
+        <v>-0.6178</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.6371</v>
+        <v>-0.6178</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3381,7 +3381,7 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.6371</v>
+        <v>-0.6178</v>
       </c>
       <c r="N64" t="n">
         <v>87</v>
@@ -3390,185 +3390,185 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Ex3rcice</t>
+          <t>Staehr</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.779</v>
+        <v>-0.8617</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.4908</v>
+        <v>-0.5429</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.9788</v>
+        <v>-0.9987</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.779</v>
+        <v>-0.8617</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.779</v>
+        <v>-0.7974</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.779</v>
+        <v>-0.7974</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.779</v>
+        <v>-0.7974</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>163</v>
+        <v>78</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.779</v>
+        <v>-0.7974</v>
       </c>
       <c r="N65" t="n">
-        <v>163</v>
+        <v>78</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Staehr</t>
+          <t>Ex3rcice</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.7974</v>
+        <v>-0.8645</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.5024</v>
+        <v>-0.5447</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.9872</v>
+        <v>-1</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.7974</v>
+        <v>-0.8645</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.7974</v>
+        <v>-0.7697000000000001</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.7974</v>
+        <v>-0.7697000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.7974</v>
+        <v>-0.7697000000000001</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>78</v>
+        <v>163</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.7974</v>
+        <v>-0.7697000000000001</v>
       </c>
       <c r="N66" t="n">
-        <v>78</v>
+        <v>163</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>HooXi</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.8222</v>
+        <v>-0.9993</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.518</v>
+        <v>-0.6296</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.9985000000000001</v>
+        <v>-1.0602</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.8222</v>
+        <v>-0.9993</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.8222</v>
+        <v>-1.1017</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.8222</v>
+        <v>-1.1017</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.8222</v>
+        <v>-1.1017</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>175</v>
+        <v>78</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.8222</v>
+        <v>-1.1017</v>
       </c>
       <c r="N67" t="n">
-        <v>175</v>
+        <v>78</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>LNZ</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.895</v>
+        <v>-1.0623</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.5639</v>
+        <v>-0.6693</v>
       </c>
       <c r="D68" t="n">
-        <v>-1.0316</v>
+        <v>-1.0883</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.895</v>
+        <v>-1.0623</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.895</v>
+        <v>-0.8225</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.895</v>
+        <v>-0.8225</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.895</v>
+        <v>-0.8225</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>87</v>
+        <v>175</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.895</v>
+        <v>-0.8225</v>
       </c>
       <c r="N68" t="n">
-        <v>87</v>
+        <v>175</v>
       </c>
     </row>
     <row r="69">
@@ -3578,28 +3578,28 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.8956</v>
+        <v>-1.1271</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.5643</v>
+        <v>-0.7101</v>
       </c>
       <c r="D69" t="n">
-        <v>-1.0319</v>
+        <v>-1.1173</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.8956</v>
+        <v>-1.1271</v>
       </c>
       <c r="F69" t="n">
-        <v>-1.042</v>
+        <v>-1.0416</v>
       </c>
       <c r="G69" t="n">
         <v>0.1464</v>
       </c>
       <c r="H69" t="n">
-        <v>-1.042</v>
+        <v>-1.0416</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.0964</v>
+        <v>-1.096</v>
       </c>
       <c r="J69" t="n">
         <v>0.1464</v>
@@ -3611,7 +3611,7 @@
         <v>82</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.9500000000000001</v>
+        <v>-0.9496000000000001</v>
       </c>
       <c r="N69" t="n">
         <v>273</v>
@@ -3620,93 +3620,93 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>HooXi</t>
+          <t>LNZ</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-1.1017</v>
+        <v>-1.2451</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.7845</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.1257</v>
+        <v>-1.17</v>
       </c>
       <c r="E70" t="n">
-        <v>-1.1017</v>
+        <v>-1.2451</v>
       </c>
       <c r="F70" t="n">
-        <v>-1.1017</v>
+        <v>-0.8954</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.1017</v>
+        <v>-0.8954</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.1017</v>
+        <v>-0.8954</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-1.1017</v>
+        <v>-0.8954</v>
       </c>
       <c r="N70" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.1035</v>
+        <v>-1.2619</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.6953</v>
+        <v>-0.7951</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.1265</v>
+        <v>-1.1775</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.1035</v>
+        <v>-1.2619</v>
       </c>
       <c r="F71" t="n">
-        <v>-1.1035</v>
+        <v>-1.3169</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-1.1035</v>
+        <v>-1.3169</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.1035</v>
+        <v>-1.3169</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-1.1035</v>
+        <v>-1.3169</v>
       </c>
       <c r="N71" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="72">
@@ -3716,28 +3716,28 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.111</v>
+        <v>-1.3945</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.7</v>
+        <v>-0.8786</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.13</v>
+        <v>-1.2367</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.111</v>
+        <v>-1.3945</v>
       </c>
       <c r="F72" t="n">
-        <v>-1.111</v>
+        <v>-1.1111</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-1.111</v>
+        <v>-1.1111</v>
       </c>
       <c r="I72" t="n">
-        <v>-1.111</v>
+        <v>-1.1111</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -3749,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-1.111</v>
+        <v>-1.1111</v>
       </c>
       <c r="N72" t="n">
         <v>87</v>
@@ -3758,32 +3758,32 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.2345</v>
+        <v>-1.3974</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.7778</v>
+        <v>-0.8804</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.1862</v>
+        <v>-1.238</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.2345</v>
+        <v>-1.3974</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.2345</v>
+        <v>-1.1037</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.2345</v>
+        <v>-1.1037</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.2345</v>
+        <v>-1.1037</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.2345</v>
+        <v>-1.1037</v>
       </c>
       <c r="N73" t="n">
         <v>76</v>
@@ -3804,47 +3804,47 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.3169</v>
+        <v>-1.4946</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.8297</v>
+        <v>-0.9417</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.2237</v>
+        <v>-1.2814</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.3169</v>
+        <v>-1.4946</v>
       </c>
       <c r="F74" t="n">
-        <v>-1.3169</v>
+        <v>-1.2352</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-1.3169</v>
+        <v>-1.2352</v>
       </c>
       <c r="I74" t="n">
-        <v>-1.3169</v>
+        <v>-1.2352</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.3169</v>
+        <v>-1.2352</v>
       </c>
       <c r="N74" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="75">
@@ -3854,28 +3854,28 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.3406</v>
+        <v>-1.6577</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.8447</v>
+        <v>-1.0444</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.2345</v>
+        <v>-1.3543</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.3406</v>
+        <v>-1.6577</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.3406</v>
+        <v>-1.3408</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.3406</v>
+        <v>-1.3408</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.3406</v>
+        <v>-1.3408</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.3406</v>
+        <v>-1.3408</v>
       </c>
       <c r="N75" t="n">
         <v>128</v>
@@ -3900,28 +3900,28 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.6145</v>
+        <v>-2.0947</v>
       </c>
       <c r="C76" t="n">
-        <v>-1.0172</v>
+        <v>-1.3198</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.3592</v>
+        <v>-1.5495</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.6145</v>
+        <v>-2.0947</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.6145</v>
+        <v>-1.6147</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.6145</v>
+        <v>-1.6147</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.6145</v>
+        <v>-1.6147</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.6145</v>
+        <v>-1.6147</v>
       </c>
       <c r="N76" t="n">
         <v>76</v>
@@ -3946,28 +3946,28 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.992</v>
+        <v>-2.2855</v>
       </c>
       <c r="C77" t="n">
-        <v>-1.2551</v>
+        <v>-1.44</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.531</v>
+        <v>-1.6347</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.992</v>
+        <v>-2.2855</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.992</v>
+        <v>-1.9917</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.992</v>
+        <v>-1.9917</v>
       </c>
       <c r="I77" t="n">
-        <v>-2.0433</v>
+        <v>-2.043</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -3979,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-2.0433</v>
+        <v>-2.043</v>
       </c>
       <c r="N77" t="n">
         <v>175</v>
@@ -3992,31 +3992,31 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-2.0536</v>
+        <v>-2.3846</v>
       </c>
       <c r="C78" t="n">
-        <v>-1.2939</v>
+        <v>-1.5024</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.559</v>
+        <v>-1.679</v>
       </c>
       <c r="E78" t="n">
-        <v>-2.0536</v>
+        <v>-2.3846</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.4334</v>
+        <v>-0.444</v>
       </c>
       <c r="G78" t="n">
-        <v>-1.6202</v>
+        <v>-1.6203</v>
       </c>
       <c r="H78" t="n">
-        <v>-0.4334</v>
+        <v>-0.444</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.456</v>
+        <v>-0.4672</v>
       </c>
       <c r="J78" t="n">
-        <v>-1.6202</v>
+        <v>-1.6203</v>
       </c>
       <c r="K78" t="n">
         <v>212</v>
@@ -4025,7 +4025,7 @@
         <v>124</v>
       </c>
       <c r="M78" t="n">
-        <v>-2.0762</v>
+        <v>-2.0875</v>
       </c>
       <c r="N78" t="n">
         <v>336</v>
@@ -4038,31 +4038,31 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.3676</v>
+        <v>-2.6058</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.4917</v>
+        <v>-1.6418</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.702</v>
+        <v>-1.7778</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.3676</v>
+        <v>-2.6058</v>
       </c>
       <c r="F79" t="n">
-        <v>-2.5224</v>
+        <v>-2.5219</v>
       </c>
       <c r="G79" t="n">
-        <v>0.1548</v>
+        <v>0.1314</v>
       </c>
       <c r="H79" t="n">
-        <v>-2.5224</v>
+        <v>-2.5219</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.3621</v>
+        <v>-1.3618</v>
       </c>
       <c r="J79" t="n">
-        <v>0.1548</v>
+        <v>0.1314</v>
       </c>
       <c r="K79" t="n">
         <v>184</v>
@@ -4071,7 +4071,7 @@
         <v>128</v>
       </c>
       <c r="M79" t="n">
-        <v>-1.2073</v>
+        <v>-1.2304</v>
       </c>
       <c r="N79" t="n">
         <v>312</v>
@@ -4084,31 +4084,31 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.5537</v>
+        <v>-2.7116</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.609</v>
+        <v>-1.7085</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.7867</v>
+        <v>-1.825</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.5537</v>
+        <v>-2.7116</v>
       </c>
       <c r="F80" t="n">
-        <v>-3.5262</v>
+        <v>-3.5256</v>
       </c>
       <c r="G80" t="n">
-        <v>0.9725</v>
+        <v>0.9724</v>
       </c>
       <c r="H80" t="n">
-        <v>-3.5262</v>
+        <v>-3.5256</v>
       </c>
       <c r="I80" t="n">
-        <v>-1.9041</v>
+        <v>-1.9038</v>
       </c>
       <c r="J80" t="n">
-        <v>0.9725</v>
+        <v>0.9724</v>
       </c>
       <c r="K80" t="n">
         <v>184</v>
@@ -4117,7 +4117,7 @@
         <v>128</v>
       </c>
       <c r="M80" t="n">
-        <v>-0.9315999999999999</v>
+        <v>-0.9313999999999999</v>
       </c>
       <c r="N80" t="n">
         <v>312</v>
@@ -4130,28 +4130,28 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.8073</v>
+        <v>-3.14</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.7688</v>
+        <v>-1.9784</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.9021</v>
+        <v>-2.0164</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.8073</v>
+        <v>-3.14</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.8073</v>
+        <v>-2.8077</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.8073</v>
+        <v>-2.8077</v>
       </c>
       <c r="I81" t="n">
-        <v>-2.8073</v>
+        <v>-2.8077</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>-2.8073</v>
+        <v>-2.8077</v>
       </c>
       <c r="N81" t="n">
         <v>139</v>
@@ -4869,10 +4869,10 @@
         <v>1.38</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7079</v>
+        <v>0.7074</v>
       </c>
       <c r="J17" t="n">
-        <v>16.9896</v>
+        <v>16.9776</v>
       </c>
     </row>
     <row r="18">
@@ -4909,10 +4909,10 @@
         <v>1.15</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3378</v>
+        <v>0.3374</v>
       </c>
       <c r="J18" t="n">
-        <v>8.107200000000001</v>
+        <v>8.0976</v>
       </c>
     </row>
     <row r="19">
@@ -4949,10 +4949,10 @@
         <v>1.03</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0961</v>
+        <v>0.0959</v>
       </c>
       <c r="J19" t="n">
-        <v>2.3064</v>
+        <v>2.3016</v>
       </c>
     </row>
     <row r="20">
@@ -4986,13 +4986,13 @@
         <v>24</v>
       </c>
       <c r="H20" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1731</v>
+        <v>-0.1622</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.1544</v>
+        <v>-3.8928</v>
       </c>
     </row>
     <row r="21">
@@ -5029,10 +5029,10 @@
         <v>0.78</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.276</v>
+        <v>-0.2762</v>
       </c>
       <c r="J21" t="n">
-        <v>-6.624</v>
+        <v>-6.6288</v>
       </c>
     </row>
     <row r="22">
@@ -5069,10 +5069,10 @@
         <v>1.54</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1988</v>
+        <v>1.1994</v>
       </c>
       <c r="J22" t="n">
-        <v>22.7772</v>
+        <v>22.7886</v>
       </c>
     </row>
     <row r="23">
@@ -5109,10 +5109,10 @@
         <v>1.28</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7046</v>
+        <v>0.7049</v>
       </c>
       <c r="J23" t="n">
-        <v>13.3874</v>
+        <v>13.3931</v>
       </c>
     </row>
     <row r="24">
@@ -5149,10 +5149,10 @@
         <v>1.19</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.5179</v>
       </c>
       <c r="J24" t="n">
-        <v>9.8344</v>
+        <v>9.8401</v>
       </c>
     </row>
     <row r="25">
@@ -5186,13 +5186,13 @@
         <v>19</v>
       </c>
       <c r="H25" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4496</v>
+        <v>0.4264</v>
       </c>
       <c r="J25" t="n">
-        <v>8.542400000000001</v>
+        <v>8.101599999999999</v>
       </c>
     </row>
     <row r="26">
@@ -5229,10 +5229,10 @@
         <v>1.08</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2483</v>
+        <v>0.2487</v>
       </c>
       <c r="J26" t="n">
-        <v>4.7177</v>
+        <v>4.7253</v>
       </c>
     </row>
     <row r="27">
@@ -5269,10 +5269,10 @@
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0251</v>
+        <v>0.0241</v>
       </c>
       <c r="J27" t="n">
-        <v>0.4769</v>
+        <v>0.4579</v>
       </c>
     </row>
     <row r="28">
@@ -5309,10 +5309,10 @@
         <v>0.9</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1361</v>
+        <v>-0.1364</v>
       </c>
       <c r="J28" t="n">
-        <v>-2.5859</v>
+        <v>-2.5916</v>
       </c>
     </row>
     <row r="29">
@@ -5349,10 +5349,10 @@
         <v>0.88</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1582</v>
+        <v>-0.1585</v>
       </c>
       <c r="J29" t="n">
-        <v>-3.0058</v>
+        <v>-3.0115</v>
       </c>
     </row>
     <row r="30">
@@ -5386,13 +5386,13 @@
         <v>19</v>
       </c>
       <c r="H30" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1991</v>
+        <v>-0.1894</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.7829</v>
+        <v>-3.5986</v>
       </c>
     </row>
     <row r="31">
@@ -5426,13 +5426,13 @@
         <v>19</v>
       </c>
       <c r="H31" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3702</v>
+        <v>-0.3616</v>
       </c>
       <c r="J31" t="n">
-        <v>-7.0338</v>
+        <v>-6.8704</v>
       </c>
     </row>
     <row r="32">
@@ -5469,10 +5469,10 @@
         <v>1.44</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7518</v>
+        <v>0.7511</v>
       </c>
       <c r="J32" t="n">
-        <v>16.5396</v>
+        <v>16.5242</v>
       </c>
     </row>
     <row r="33">
@@ -5509,10 +5509,10 @@
         <v>1.1</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2818</v>
+        <v>0.2812</v>
       </c>
       <c r="J33" t="n">
-        <v>6.1996</v>
+        <v>6.1864</v>
       </c>
     </row>
     <row r="34">
@@ -5546,13 +5546,13 @@
         <v>22</v>
       </c>
       <c r="H34" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2602</v>
+        <v>-0.2506</v>
       </c>
       <c r="J34" t="n">
-        <v>-5.7244</v>
+        <v>-5.5132</v>
       </c>
     </row>
     <row r="35">
@@ -5589,10 +5589,10 @@
         <v>0.61</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4171</v>
+        <v>-0.4173</v>
       </c>
       <c r="J35" t="n">
-        <v>-9.1762</v>
+        <v>-9.1806</v>
       </c>
     </row>
     <row r="36">
@@ -5629,10 +5629,10 @@
         <v>0.45</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5555</v>
+        <v>-0.5556</v>
       </c>
       <c r="J36" t="n">
-        <v>-12.221</v>
+        <v>-12.2232</v>
       </c>
     </row>
     <row r="37">
@@ -6469,10 +6469,10 @@
         <v>1.47</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7337</v>
+        <v>0.7332</v>
       </c>
       <c r="J57" t="n">
-        <v>17.6088</v>
+        <v>17.5968</v>
       </c>
     </row>
     <row r="58">
@@ -6509,10 +6509,10 @@
         <v>1.06</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1638</v>
+        <v>0.1636</v>
       </c>
       <c r="J58" t="n">
-        <v>3.9312</v>
+        <v>3.9264</v>
       </c>
     </row>
     <row r="59">
@@ -6546,13 +6546,13 @@
         <v>24</v>
       </c>
       <c r="H59" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0385</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="J59" t="n">
-        <v>0.924</v>
+        <v>1.644</v>
       </c>
     </row>
     <row r="60">
@@ -6589,10 +6589,10 @@
         <v>1</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.0031</v>
+        <v>-0.0033</v>
       </c>
       <c r="J60" t="n">
-        <v>-0.07439999999999999</v>
+        <v>-0.07920000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -6629,10 +6629,10 @@
         <v>0.72</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3337</v>
+        <v>-0.3338</v>
       </c>
       <c r="J61" t="n">
-        <v>-8.008800000000001</v>
+        <v>-8.011200000000001</v>
       </c>
     </row>
     <row r="62">
@@ -6669,10 +6669,10 @@
         <v>1.37</v>
       </c>
       <c r="I62" t="n">
-        <v>0.5238</v>
+        <v>0.5234</v>
       </c>
       <c r="J62" t="n">
-        <v>11.5236</v>
+        <v>11.5148</v>
       </c>
     </row>
     <row r="63">
@@ -6706,13 +6706,13 @@
         <v>22</v>
       </c>
       <c r="H63" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2997</v>
+        <v>0.3131</v>
       </c>
       <c r="J63" t="n">
-        <v>6.5934</v>
+        <v>6.8882</v>
       </c>
     </row>
     <row r="64">
@@ -6749,10 +6749,10 @@
         <v>1</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0002</v>
+        <v>0.0001</v>
       </c>
       <c r="J64" t="n">
-        <v>0.0044</v>
+        <v>0.0022</v>
       </c>
     </row>
     <row r="65">
@@ -6789,10 +6789,10 @@
         <v>0.75</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3006</v>
+        <v>-0.3008</v>
       </c>
       <c r="J65" t="n">
-        <v>-6.6132</v>
+        <v>-6.6176</v>
       </c>
     </row>
     <row r="66">
@@ -6829,10 +6829,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3565</v>
+        <v>-0.3567</v>
       </c>
       <c r="J66" t="n">
-        <v>-7.843</v>
+        <v>-7.8474</v>
       </c>
     </row>
     <row r="67">
@@ -8106,13 +8106,13 @@
         <v>23</v>
       </c>
       <c r="H98" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="I98" t="n">
-        <v>0.4119</v>
+        <v>0.4226</v>
       </c>
       <c r="J98" t="n">
-        <v>9.473699999999999</v>
+        <v>9.719799999999999</v>
       </c>
     </row>
     <row r="99">
@@ -8146,13 +8146,13 @@
         <v>23</v>
       </c>
       <c r="H99" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="I99" t="n">
-        <v>0.101</v>
+        <v>0.0837</v>
       </c>
       <c r="J99" t="n">
-        <v>2.323</v>
+        <v>1.9251</v>
       </c>
     </row>
     <row r="100">
@@ -8269,10 +8269,10 @@
         <v>1.47</v>
       </c>
       <c r="I102" t="n">
-        <v>0.9215</v>
+        <v>0.921</v>
       </c>
       <c r="J102" t="n">
-        <v>22.116</v>
+        <v>22.104</v>
       </c>
     </row>
     <row r="103">
@@ -8309,10 +8309,10 @@
         <v>1.43</v>
       </c>
       <c r="I103" t="n">
-        <v>0.8652</v>
+        <v>0.8647</v>
       </c>
       <c r="J103" t="n">
-        <v>20.7648</v>
+        <v>20.7528</v>
       </c>
     </row>
     <row r="104">
@@ -8349,10 +8349,10 @@
         <v>1.24</v>
       </c>
       <c r="I104" t="n">
-        <v>0.5831</v>
+        <v>0.5828</v>
       </c>
       <c r="J104" t="n">
-        <v>13.9944</v>
+        <v>13.9872</v>
       </c>
     </row>
     <row r="105">
@@ -8386,13 +8386,13 @@
         <v>24</v>
       </c>
       <c r="H105" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0312</v>
+        <v>0.0722</v>
       </c>
       <c r="J105" t="n">
-        <v>0.7488</v>
+        <v>1.7328</v>
       </c>
     </row>
     <row r="106">
@@ -8429,10 +8429,10 @@
         <v>0.71</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.8193</v>
+        <v>-0.8196</v>
       </c>
       <c r="J106" t="n">
-        <v>-19.6632</v>
+        <v>-19.6704</v>
       </c>
     </row>
     <row r="107">
@@ -9869,10 +9869,10 @@
         <v>1.35</v>
       </c>
       <c r="I142" t="n">
-        <v>0.6875</v>
+        <v>0.6869</v>
       </c>
       <c r="J142" t="n">
-        <v>20.625</v>
+        <v>20.607</v>
       </c>
     </row>
     <row r="143">
@@ -9906,13 +9906,13 @@
         <v>30</v>
       </c>
       <c r="H143" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="I143" t="n">
-        <v>0.4433</v>
+        <v>0.4599</v>
       </c>
       <c r="J143" t="n">
-        <v>13.299</v>
+        <v>13.797</v>
       </c>
     </row>
     <row r="144">
@@ -9949,10 +9949,10 @@
         <v>0.92</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1206</v>
+        <v>-0.1207</v>
       </c>
       <c r="J144" t="n">
-        <v>-3.618</v>
+        <v>-3.621</v>
       </c>
     </row>
     <row r="145">
@@ -9989,10 +9989,10 @@
         <v>0.79</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2588</v>
+        <v>-0.259</v>
       </c>
       <c r="J145" t="n">
-        <v>-7.764</v>
+        <v>-7.77</v>
       </c>
     </row>
     <row r="146">
@@ -10029,10 +10029,10 @@
         <v>0.55</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4775</v>
+        <v>-0.4776</v>
       </c>
       <c r="J146" t="n">
-        <v>-14.325</v>
+        <v>-14.328</v>
       </c>
     </row>
     <row r="147">
@@ -11866,13 +11866,13 @@
         <v>19</v>
       </c>
       <c r="H192" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="I192" t="n">
-        <v>0.4553</v>
+        <v>0.4721</v>
       </c>
       <c r="J192" t="n">
-        <v>8.650700000000001</v>
+        <v>8.969900000000001</v>
       </c>
     </row>
     <row r="193">
@@ -11909,10 +11909,10 @@
         <v>0.9</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.1405</v>
+        <v>-0.1406</v>
       </c>
       <c r="J193" t="n">
-        <v>-2.6695</v>
+        <v>-2.6714</v>
       </c>
     </row>
     <row r="194">
@@ -11949,10 +11949,10 @@
         <v>0.88</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1624</v>
+        <v>-0.1626</v>
       </c>
       <c r="J194" t="n">
-        <v>-3.0856</v>
+        <v>-3.0894</v>
       </c>
     </row>
     <row r="195">
@@ -11989,10 +11989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.235</v>
+        <v>-0.2351</v>
       </c>
       <c r="J195" t="n">
-        <v>-4.465</v>
+        <v>-4.4669</v>
       </c>
     </row>
     <row r="196">
@@ -12029,10 +12029,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.235</v>
+        <v>-0.2351</v>
       </c>
       <c r="J196" t="n">
-        <v>-4.465</v>
+        <v>-4.4669</v>
       </c>
     </row>
     <row r="197">
@@ -12069,10 +12069,10 @@
         <v>1.51</v>
       </c>
       <c r="I197" t="n">
-        <v>1.1175</v>
+        <v>1.118</v>
       </c>
       <c r="J197" t="n">
-        <v>21.2325</v>
+        <v>21.242</v>
       </c>
     </row>
     <row r="198">
@@ -12106,13 +12106,13 @@
         <v>19</v>
       </c>
       <c r="H198" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="I198" t="n">
-        <v>1.0761</v>
+        <v>1.0623</v>
       </c>
       <c r="J198" t="n">
-        <v>20.4459</v>
+        <v>20.1837</v>
       </c>
     </row>
     <row r="199">
@@ -12149,10 +12149,10 @@
         <v>1.2</v>
       </c>
       <c r="I199" t="n">
-        <v>0.5451</v>
+        <v>0.5452</v>
       </c>
       <c r="J199" t="n">
-        <v>10.3569</v>
+        <v>10.3588</v>
       </c>
     </row>
     <row r="200">
@@ -12189,10 +12189,10 @@
         <v>0.95</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2376</v>
+        <v>-0.2373</v>
       </c>
       <c r="J200" t="n">
-        <v>-4.5144</v>
+        <v>-4.5087</v>
       </c>
     </row>
     <row r="201">
@@ -12229,10 +12229,10 @@
         <v>0.87</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.458</v>
+        <v>-0.4577</v>
       </c>
       <c r="J201" t="n">
-        <v>-8.702</v>
+        <v>-8.696300000000001</v>
       </c>
     </row>
     <row r="202">
@@ -12266,13 +12266,13 @@
         <v>18</v>
       </c>
       <c r="H202" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="I202" t="n">
-        <v>1.1547</v>
+        <v>1.1645</v>
       </c>
       <c r="J202" t="n">
-        <v>20.7846</v>
+        <v>20.961</v>
       </c>
     </row>
     <row r="203">
@@ -12309,10 +12309,10 @@
         <v>0.88</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.1575</v>
+        <v>-0.1577</v>
       </c>
       <c r="J203" t="n">
-        <v>-2.835</v>
+        <v>-2.8386</v>
       </c>
     </row>
     <row r="204">
@@ -12349,10 +12349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.342</v>
+        <v>-0.3422</v>
       </c>
       <c r="J204" t="n">
-        <v>-6.156</v>
+        <v>-6.1596</v>
       </c>
     </row>
     <row r="205">
@@ -12389,10 +12389,10 @@
         <v>0.64</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3874</v>
+        <v>-0.3877</v>
       </c>
       <c r="J205" t="n">
-        <v>-6.9732</v>
+        <v>-6.9786</v>
       </c>
     </row>
     <row r="206">
@@ -12429,10 +12429,10 @@
         <v>0.37</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.6203</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="J206" t="n">
-        <v>-11.1654</v>
+        <v>-11.169</v>
       </c>
     </row>
     <row r="207">
@@ -13666,13 +13666,13 @@
         <v>16</v>
       </c>
       <c r="H237" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="I237" t="n">
-        <v>1.6707</v>
+        <v>1.6595</v>
       </c>
       <c r="J237" t="n">
-        <v>26.7312</v>
+        <v>26.552</v>
       </c>
     </row>
     <row r="238">
@@ -13709,10 +13709,10 @@
         <v>1.58</v>
       </c>
       <c r="I238" t="n">
-        <v>1.1644</v>
+        <v>1.1646</v>
       </c>
       <c r="J238" t="n">
-        <v>18.6304</v>
+        <v>18.6336</v>
       </c>
     </row>
     <row r="239">
@@ -13749,10 +13749,10 @@
         <v>1.38</v>
       </c>
       <c r="I239" t="n">
-        <v>0.8703</v>
+        <v>0.8706</v>
       </c>
       <c r="J239" t="n">
-        <v>13.9248</v>
+        <v>13.9296</v>
       </c>
     </row>
     <row r="240">
@@ -13789,10 +13789,10 @@
         <v>1.35</v>
       </c>
       <c r="I240" t="n">
-        <v>0.8133</v>
+        <v>0.8136</v>
       </c>
       <c r="J240" t="n">
-        <v>13.0128</v>
+        <v>13.0176</v>
       </c>
     </row>
     <row r="241">
@@ -13829,10 +13829,10 @@
         <v>1.13</v>
       </c>
       <c r="I241" t="n">
-        <v>0.3416</v>
+        <v>0.3418</v>
       </c>
       <c r="J241" t="n">
-        <v>5.4656</v>
+        <v>5.4688</v>
       </c>
     </row>
     <row r="242">
@@ -14669,10 +14669,10 @@
         <v>2.25</v>
       </c>
       <c r="I262" t="n">
-        <v>1.9193</v>
+        <v>1.9197</v>
       </c>
       <c r="J262" t="n">
-        <v>26.8702</v>
+        <v>26.8758</v>
       </c>
     </row>
     <row r="263">
@@ -14706,13 +14706,13 @@
         <v>14</v>
       </c>
       <c r="H263" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="I263" t="n">
-        <v>1.4588</v>
+        <v>1.4475</v>
       </c>
       <c r="J263" t="n">
-        <v>20.4232</v>
+        <v>20.265</v>
       </c>
     </row>
     <row r="264">
@@ -14749,10 +14749,10 @@
         <v>1.78</v>
       </c>
       <c r="I264" t="n">
-        <v>1.3891</v>
+        <v>1.3893</v>
       </c>
       <c r="J264" t="n">
-        <v>19.4474</v>
+        <v>19.4502</v>
       </c>
     </row>
     <row r="265">
@@ -14789,10 +14789,10 @@
         <v>1.31</v>
       </c>
       <c r="I265" t="n">
-        <v>0.7127</v>
+        <v>0.713</v>
       </c>
       <c r="J265" t="n">
-        <v>9.9778</v>
+        <v>9.981999999999999</v>
       </c>
     </row>
     <row r="266">
@@ -14829,10 +14829,10 @@
         <v>1.1</v>
       </c>
       <c r="I266" t="n">
-        <v>0.2434</v>
+        <v>0.2437</v>
       </c>
       <c r="J266" t="n">
-        <v>3.4076</v>
+        <v>3.4118</v>
       </c>
     </row>
     <row r="267">
@@ -14869,10 +14869,10 @@
         <v>1.43</v>
       </c>
       <c r="I267" t="n">
-        <v>0.9537</v>
+        <v>0.9520999999999999</v>
       </c>
       <c r="J267" t="n">
-        <v>13.3518</v>
+        <v>13.3294</v>
       </c>
     </row>
     <row r="268">
@@ -14909,10 +14909,10 @@
         <v>0.75</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.273</v>
+        <v>-0.2733</v>
       </c>
       <c r="J268" t="n">
-        <v>-3.822</v>
+        <v>-3.8262</v>
       </c>
     </row>
     <row r="269">
@@ -14946,13 +14946,13 @@
         <v>14</v>
       </c>
       <c r="H269" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.4599</v>
+        <v>-0.4514</v>
       </c>
       <c r="J269" t="n">
-        <v>-6.4386</v>
+        <v>-6.3196</v>
       </c>
     </row>
     <row r="270">
@@ -14989,10 +14989,10 @@
         <v>0.44</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.5473</v>
+        <v>-0.5476</v>
       </c>
       <c r="J270" t="n">
-        <v>-7.6622</v>
+        <v>-7.6664</v>
       </c>
     </row>
     <row r="271">
@@ -15029,10 +15029,10 @@
         <v>0.38</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.5992</v>
+        <v>-0.5994</v>
       </c>
       <c r="J271" t="n">
-        <v>-8.3888</v>
+        <v>-8.3916</v>
       </c>
     </row>
     <row r="272">
@@ -15666,13 +15666,13 @@
         <v>24</v>
       </c>
       <c r="H287" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="I287" t="n">
-        <v>1.2337</v>
+        <v>1.2206</v>
       </c>
       <c r="J287" t="n">
-        <v>29.6088</v>
+        <v>29.2944</v>
       </c>
     </row>
     <row r="288">
@@ -15709,10 +15709,10 @@
         <v>1.46</v>
       </c>
       <c r="I288" t="n">
-        <v>1.0662</v>
+        <v>1.0668</v>
       </c>
       <c r="J288" t="n">
-        <v>25.5888</v>
+        <v>25.6032</v>
       </c>
     </row>
     <row r="289">
@@ -15749,10 +15749,10 @@
         <v>1.11</v>
       </c>
       <c r="I289" t="n">
-        <v>0.3472</v>
+        <v>0.3475</v>
       </c>
       <c r="J289" t="n">
-        <v>8.332800000000001</v>
+        <v>8.34</v>
       </c>
     </row>
     <row r="290">
@@ -15789,10 +15789,10 @@
         <v>0.82</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.5651</v>
+        <v>-0.5647</v>
       </c>
       <c r="J290" t="n">
-        <v>-13.5624</v>
+        <v>-13.5528</v>
       </c>
     </row>
     <row r="291">
@@ -15829,10 +15829,10 @@
         <v>0.64</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.9573</v>
+        <v>-0.957</v>
       </c>
       <c r="J291" t="n">
-        <v>-22.9752</v>
+        <v>-22.968</v>
       </c>
     </row>
     <row r="292">
@@ -17469,10 +17469,10 @@
         <v>1.03</v>
       </c>
       <c r="I332" t="n">
-        <v>0.1206</v>
+        <v>0.1201</v>
       </c>
       <c r="J332" t="n">
-        <v>2.7738</v>
+        <v>2.7623</v>
       </c>
     </row>
     <row r="333">
@@ -17506,13 +17506,13 @@
         <v>23</v>
       </c>
       <c r="H333" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="I333" t="n">
-        <v>0.0175</v>
+        <v>0.0616</v>
       </c>
       <c r="J333" t="n">
-        <v>0.4025</v>
+        <v>1.4168</v>
       </c>
     </row>
     <row r="334">
@@ -17549,10 +17549,10 @@
         <v>0.98</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.0338</v>
+        <v>-0.034</v>
       </c>
       <c r="J334" t="n">
-        <v>-0.7774</v>
+        <v>-0.782</v>
       </c>
     </row>
     <row r="335">
@@ -17589,10 +17589,10 @@
         <v>0.83</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.2119</v>
+        <v>-0.212</v>
       </c>
       <c r="J335" t="n">
-        <v>-4.8737</v>
+        <v>-4.876</v>
       </c>
     </row>
     <row r="336">
@@ -17629,10 +17629,10 @@
         <v>0.6</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.4272</v>
+        <v>-0.4274</v>
       </c>
       <c r="J336" t="n">
-        <v>-9.8256</v>
+        <v>-9.8302</v>
       </c>
     </row>
     <row r="337">
@@ -18866,13 +18866,13 @@
         <v>23</v>
       </c>
       <c r="H367" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="I367" t="n">
-        <v>1.1568</v>
+        <v>1.1435</v>
       </c>
       <c r="J367" t="n">
-        <v>26.6064</v>
+        <v>26.3005</v>
       </c>
     </row>
     <row r="368">
@@ -18909,10 +18909,10 @@
         <v>1.36</v>
       </c>
       <c r="I368" t="n">
-        <v>0.8842</v>
+        <v>0.8847</v>
       </c>
       <c r="J368" t="n">
-        <v>20.3366</v>
+        <v>20.3481</v>
       </c>
     </row>
     <row r="369">
@@ -18949,10 +18949,10 @@
         <v>1.06</v>
       </c>
       <c r="I369" t="n">
-        <v>0.2078</v>
+        <v>0.2081</v>
       </c>
       <c r="J369" t="n">
-        <v>4.7794</v>
+        <v>4.7863</v>
       </c>
     </row>
     <row r="370">
@@ -18989,10 +18989,10 @@
         <v>0.92</v>
       </c>
       <c r="I370" t="n">
-        <v>-0.3169</v>
+        <v>-0.3165</v>
       </c>
       <c r="J370" t="n">
-        <v>-7.2887</v>
+        <v>-7.2795</v>
       </c>
     </row>
     <row r="371">
@@ -19029,10 +19029,10 @@
         <v>0.89</v>
       </c>
       <c r="I371" t="n">
-        <v>-0.3979</v>
+        <v>-0.3975</v>
       </c>
       <c r="J371" t="n">
-        <v>-9.1517</v>
+        <v>-9.1425</v>
       </c>
     </row>
     <row r="372">
@@ -19466,13 +19466,13 @@
         <v>17</v>
       </c>
       <c r="H382" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="I382" t="n">
-        <v>1.4633</v>
+        <v>1.4515</v>
       </c>
       <c r="J382" t="n">
-        <v>24.8761</v>
+        <v>24.6755</v>
       </c>
     </row>
     <row r="383">
@@ -19509,10 +19509,10 @@
         <v>1.52</v>
       </c>
       <c r="I383" t="n">
-        <v>1.0981</v>
+        <v>1.0984</v>
       </c>
       <c r="J383" t="n">
-        <v>18.6677</v>
+        <v>18.6728</v>
       </c>
     </row>
     <row r="384">
@@ -19549,10 +19549,10 @@
         <v>1.31</v>
       </c>
       <c r="I384" t="n">
-        <v>0.7477</v>
+        <v>0.7479</v>
       </c>
       <c r="J384" t="n">
-        <v>12.7109</v>
+        <v>12.7143</v>
       </c>
     </row>
     <row r="385">
@@ -19589,10 +19589,10 @@
         <v>1.21</v>
       </c>
       <c r="I385" t="n">
-        <v>0.5402</v>
+        <v>0.5405</v>
       </c>
       <c r="J385" t="n">
-        <v>9.183400000000001</v>
+        <v>9.188499999999999</v>
       </c>
     </row>
     <row r="386">
@@ -19629,10 +19629,10 @@
         <v>1.13</v>
       </c>
       <c r="I386" t="n">
-        <v>0.3551</v>
+        <v>0.3554</v>
       </c>
       <c r="J386" t="n">
-        <v>6.0367</v>
+        <v>6.0418</v>
       </c>
     </row>
     <row r="387">
@@ -21069,10 +21069,10 @@
         <v>1.1</v>
       </c>
       <c r="I422" t="n">
-        <v>0.2673</v>
+        <v>0.2668</v>
       </c>
       <c r="J422" t="n">
-        <v>4.8114</v>
+        <v>4.8024</v>
       </c>
     </row>
     <row r="423">
@@ -21106,13 +21106,13 @@
         <v>18</v>
       </c>
       <c r="H423" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I423" t="n">
-        <v>0.1366</v>
+        <v>0.16</v>
       </c>
       <c r="J423" t="n">
-        <v>2.4588</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="424">
@@ -21149,10 +21149,10 @@
         <v>1.03</v>
       </c>
       <c r="I424" t="n">
-        <v>0.1114</v>
+        <v>0.111</v>
       </c>
       <c r="J424" t="n">
-        <v>2.0052</v>
+        <v>1.998</v>
       </c>
     </row>
     <row r="425">
@@ -21189,10 +21189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I425" t="n">
-        <v>-0.0946</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="J425" t="n">
-        <v>-1.7028</v>
+        <v>-1.7046</v>
       </c>
     </row>
     <row r="426">
@@ -21229,10 +21229,10 @@
         <v>0.54</v>
       </c>
       <c r="I426" t="n">
-        <v>-0.4834</v>
+        <v>-0.4835</v>
       </c>
       <c r="J426" t="n">
-        <v>-8.7012</v>
+        <v>-8.702999999999999</v>
       </c>
     </row>
     <row r="427">
@@ -21269,10 +21269,10 @@
         <v>1.39</v>
       </c>
       <c r="I427" t="n">
-        <v>0.9313</v>
+        <v>0.9317</v>
       </c>
       <c r="J427" t="n">
-        <v>16.7634</v>
+        <v>16.7706</v>
       </c>
     </row>
     <row r="428">
@@ -21306,13 +21306,13 @@
         <v>18</v>
       </c>
       <c r="H428" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="I428" t="n">
-        <v>0.8339</v>
+        <v>0.8144</v>
       </c>
       <c r="J428" t="n">
-        <v>15.0102</v>
+        <v>14.6592</v>
       </c>
     </row>
     <row r="429">
@@ -21349,10 +21349,10 @@
         <v>1.2</v>
       </c>
       <c r="I429" t="n">
-        <v>0.5455</v>
+        <v>0.5457</v>
       </c>
       <c r="J429" t="n">
-        <v>9.819000000000001</v>
+        <v>9.8226</v>
       </c>
     </row>
     <row r="430">
@@ -21389,10 +21389,10 @@
         <v>1.15</v>
       </c>
       <c r="I430" t="n">
-        <v>0.4341</v>
+        <v>0.4344</v>
       </c>
       <c r="J430" t="n">
-        <v>7.8138</v>
+        <v>7.8192</v>
       </c>
     </row>
     <row r="431">
@@ -21429,10 +21429,10 @@
         <v>0.9</v>
       </c>
       <c r="I431" t="n">
-        <v>-0.3794</v>
+        <v>-0.3791</v>
       </c>
       <c r="J431" t="n">
-        <v>-6.8292</v>
+        <v>-6.8238</v>
       </c>
     </row>
     <row r="432">
@@ -22066,13 +22066,13 @@
         <v>19</v>
       </c>
       <c r="H447" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="I447" t="n">
-        <v>0.3609</v>
+        <v>0.3746</v>
       </c>
       <c r="J447" t="n">
-        <v>6.8571</v>
+        <v>7.1174</v>
       </c>
     </row>
     <row r="448">
@@ -22109,10 +22109,10 @@
         <v>0.88</v>
       </c>
       <c r="I448" t="n">
-        <v>-0.1532</v>
+        <v>-0.1534</v>
       </c>
       <c r="J448" t="n">
-        <v>-2.9108</v>
+        <v>-2.9146</v>
       </c>
     </row>
     <row r="449">
@@ -22149,10 +22149,10 @@
         <v>0.68</v>
       </c>
       <c r="I449" t="n">
-        <v>-0.3468</v>
+        <v>-0.347</v>
       </c>
       <c r="J449" t="n">
-        <v>-6.5892</v>
+        <v>-6.593</v>
       </c>
     </row>
     <row r="450">
@@ -22189,10 +22189,10 @@
         <v>0.65</v>
       </c>
       <c r="I450" t="n">
-        <v>-0.374</v>
+        <v>-0.3743</v>
       </c>
       <c r="J450" t="n">
-        <v>-7.106</v>
+        <v>-7.1117</v>
       </c>
     </row>
     <row r="451">
@@ -22229,10 +22229,10 @@
         <v>0.65</v>
       </c>
       <c r="I451" t="n">
-        <v>-0.374</v>
+        <v>-0.3743</v>
       </c>
       <c r="J451" t="n">
-        <v>-7.106</v>
+        <v>-7.1117</v>
       </c>
     </row>
     <row r="452">
@@ -23666,13 +23666,13 @@
         <v>22</v>
       </c>
       <c r="H487" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="I487" t="n">
-        <v>1.4549</v>
+        <v>1.4426</v>
       </c>
       <c r="J487" t="n">
-        <v>32.0078</v>
+        <v>31.7372</v>
       </c>
     </row>
     <row r="488">
@@ -23709,10 +23709,10 @@
         <v>1.28</v>
       </c>
       <c r="I488" t="n">
-        <v>0.716</v>
+        <v>0.7164</v>
       </c>
       <c r="J488" t="n">
-        <v>15.752</v>
+        <v>15.7608</v>
       </c>
     </row>
     <row r="489">
@@ -23749,10 +23749,10 @@
         <v>1.21</v>
       </c>
       <c r="I489" t="n">
-        <v>0.5687</v>
+        <v>0.569</v>
       </c>
       <c r="J489" t="n">
-        <v>12.5114</v>
+        <v>12.518</v>
       </c>
     </row>
     <row r="490">
@@ -23789,10 +23789,10 @@
         <v>0.93</v>
       </c>
       <c r="I490" t="n">
-        <v>-0.2936</v>
+        <v>-0.2932</v>
       </c>
       <c r="J490" t="n">
-        <v>-6.4592</v>
+        <v>-6.4504</v>
       </c>
     </row>
     <row r="491">
@@ -23829,10 +23829,10 @@
         <v>0.72</v>
       </c>
       <c r="I491" t="n">
-        <v>-0.7992</v>
+        <v>-0.7989000000000001</v>
       </c>
       <c r="J491" t="n">
-        <v>-17.5824</v>
+        <v>-17.5758</v>
       </c>
     </row>
     <row r="492">
@@ -24469,10 +24469,10 @@
         <v>1.16</v>
       </c>
       <c r="I507" t="n">
-        <v>0.3852</v>
+        <v>0.3846</v>
       </c>
       <c r="J507" t="n">
-        <v>8.0892</v>
+        <v>8.076599999999999</v>
       </c>
     </row>
     <row r="508">
@@ -24506,13 +24506,13 @@
         <v>21</v>
       </c>
       <c r="H508" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="I508" t="n">
-        <v>0.2708</v>
+        <v>0.2901</v>
       </c>
       <c r="J508" t="n">
-        <v>5.6868</v>
+        <v>6.0921</v>
       </c>
     </row>
     <row r="509">
@@ -24549,10 +24549,10 @@
         <v>1.01</v>
       </c>
       <c r="I509" t="n">
-        <v>0.0561</v>
+        <v>0.0557</v>
       </c>
       <c r="J509" t="n">
-        <v>1.1781</v>
+        <v>1.1697</v>
       </c>
     </row>
     <row r="510">
@@ -24589,10 +24589,10 @@
         <v>0.74</v>
       </c>
       <c r="I510" t="n">
-        <v>-0.3025</v>
+        <v>-0.3027</v>
       </c>
       <c r="J510" t="n">
-        <v>-6.3525</v>
+        <v>-6.3567</v>
       </c>
     </row>
     <row r="511">
@@ -24629,10 +24629,10 @@
         <v>0.57</v>
       </c>
       <c r="I511" t="n">
-        <v>-0.4562</v>
+        <v>-0.4563</v>
       </c>
       <c r="J511" t="n">
-        <v>-9.5802</v>
+        <v>-9.5823</v>
       </c>
     </row>
     <row r="512">
@@ -24869,10 +24869,10 @@
         <v>1.2</v>
       </c>
       <c r="I517" t="n">
-        <v>0.4964</v>
+        <v>0.4955</v>
       </c>
       <c r="J517" t="n">
-        <v>9.928000000000001</v>
+        <v>9.91</v>
       </c>
     </row>
     <row r="518">
@@ -24909,10 +24909,10 @@
         <v>1</v>
       </c>
       <c r="I518" t="n">
-        <v>0.0381</v>
+        <v>0.0374</v>
       </c>
       <c r="J518" t="n">
-        <v>0.762</v>
+        <v>0.748</v>
       </c>
     </row>
     <row r="519">
@@ -24946,13 +24946,13 @@
         <v>20</v>
       </c>
       <c r="H519" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="I519" t="n">
-        <v>-0.3833</v>
+        <v>-0.3745</v>
       </c>
       <c r="J519" t="n">
-        <v>-7.666</v>
+        <v>-7.49</v>
       </c>
     </row>
     <row r="520">
@@ -24989,10 +24989,10 @@
         <v>0.63</v>
       </c>
       <c r="I520" t="n">
-        <v>-0.3923</v>
+        <v>-0.3925</v>
       </c>
       <c r="J520" t="n">
-        <v>-7.846</v>
+        <v>-7.85</v>
       </c>
     </row>
     <row r="521">
@@ -25029,10 +25029,10 @@
         <v>0.58</v>
       </c>
       <c r="I521" t="n">
-        <v>-0.4368</v>
+        <v>-0.437</v>
       </c>
       <c r="J521" t="n">
-        <v>-8.736000000000001</v>
+        <v>-8.74</v>
       </c>
     </row>
     <row r="522">
@@ -25069,10 +25069,10 @@
         <v>1.31</v>
       </c>
       <c r="I522" t="n">
-        <v>0.8151</v>
+        <v>0.8158</v>
       </c>
       <c r="J522" t="n">
-        <v>17.9322</v>
+        <v>17.9476</v>
       </c>
     </row>
     <row r="523">
@@ -25106,13 +25106,13 @@
         <v>22</v>
       </c>
       <c r="H523" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="I523" t="n">
-        <v>0.7941</v>
+        <v>0.7735</v>
       </c>
       <c r="J523" t="n">
-        <v>17.4702</v>
+        <v>17.017</v>
       </c>
     </row>
     <row r="524">
@@ -25149,10 +25149,10 @@
         <v>0.95</v>
       </c>
       <c r="I524" t="n">
-        <v>-0.208</v>
+        <v>-0.2076</v>
       </c>
       <c r="J524" t="n">
-        <v>-4.576</v>
+        <v>-4.5672</v>
       </c>
     </row>
     <row r="525">
@@ -25189,10 +25189,10 @@
         <v>0.84</v>
       </c>
       <c r="I525" t="n">
-        <v>-0.5018</v>
+        <v>-0.5014</v>
       </c>
       <c r="J525" t="n">
-        <v>-11.0396</v>
+        <v>-11.0308</v>
       </c>
     </row>
     <row r="526">
@@ -25229,10 +25229,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I526" t="n">
-        <v>-0.5729</v>
+        <v>-0.5725</v>
       </c>
       <c r="J526" t="n">
-        <v>-12.6038</v>
+        <v>-12.595</v>
       </c>
     </row>
     <row r="527">
@@ -28469,10 +28469,10 @@
         <v>1.46</v>
       </c>
       <c r="I607" t="n">
-        <v>0.9176</v>
+        <v>0.9153</v>
       </c>
       <c r="J607" t="n">
-        <v>13.764</v>
+        <v>13.7295</v>
       </c>
     </row>
     <row r="608">
@@ -28506,13 +28506,13 @@
         <v>15</v>
       </c>
       <c r="H608" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="I608" t="n">
-        <v>0.8075</v>
+        <v>0.8372000000000001</v>
       </c>
       <c r="J608" t="n">
-        <v>12.1125</v>
+        <v>12.558</v>
       </c>
     </row>
     <row r="609">
@@ -28549,10 +28549,10 @@
         <v>0.5</v>
       </c>
       <c r="I609" t="n">
-        <v>-0.5086000000000001</v>
+        <v>-0.509</v>
       </c>
       <c r="J609" t="n">
-        <v>-7.629</v>
+        <v>-7.635</v>
       </c>
     </row>
     <row r="610">
@@ -28589,10 +28589,10 @@
         <v>0.46</v>
       </c>
       <c r="I610" t="n">
-        <v>-0.5429</v>
+        <v>-0.5433</v>
       </c>
       <c r="J610" t="n">
-        <v>-8.1435</v>
+        <v>-8.1495</v>
       </c>
     </row>
     <row r="611">
@@ -28629,10 +28629,10 @@
         <v>0.34</v>
       </c>
       <c r="I611" t="n">
-        <v>-0.6439</v>
+        <v>-0.6442</v>
       </c>
       <c r="J611" t="n">
-        <v>-9.6585</v>
+        <v>-9.663</v>
       </c>
     </row>
     <row r="612">
@@ -28669,10 +28669,10 @@
         <v>1.32</v>
       </c>
       <c r="I612" t="n">
-        <v>0.8011</v>
+        <v>0.8015</v>
       </c>
       <c r="J612" t="n">
-        <v>18.4253</v>
+        <v>18.4345</v>
       </c>
     </row>
     <row r="613">
@@ -28709,10 +28709,10 @@
         <v>1.3</v>
       </c>
       <c r="I613" t="n">
-        <v>0.7604</v>
+        <v>0.7608</v>
       </c>
       <c r="J613" t="n">
-        <v>17.4892</v>
+        <v>17.4984</v>
       </c>
     </row>
     <row r="614">
@@ -28749,10 +28749,10 @@
         <v>1.1</v>
       </c>
       <c r="I614" t="n">
-        <v>0.3159</v>
+        <v>0.3163</v>
       </c>
       <c r="J614" t="n">
-        <v>7.2657</v>
+        <v>7.2749</v>
       </c>
     </row>
     <row r="615">
@@ -28786,13 +28786,13 @@
         <v>23</v>
       </c>
       <c r="H615" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="I615" t="n">
-        <v>0.2897</v>
+        <v>0.2629</v>
       </c>
       <c r="J615" t="n">
-        <v>6.6631</v>
+        <v>6.0467</v>
       </c>
     </row>
     <row r="616">
@@ -28829,10 +28829,10 @@
         <v>1.01</v>
       </c>
       <c r="I616" t="n">
-        <v>0.0326</v>
+        <v>0.033</v>
       </c>
       <c r="J616" t="n">
-        <v>0.7498</v>
+        <v>0.759</v>
       </c>
     </row>
     <row r="617">
@@ -28869,10 +28869,10 @@
         <v>1.12</v>
       </c>
       <c r="I617" t="n">
-        <v>0.2953</v>
+        <v>0.2941</v>
       </c>
       <c r="J617" t="n">
-        <v>6.7919</v>
+        <v>6.7643</v>
       </c>
     </row>
     <row r="618">
@@ -28906,13 +28906,13 @@
         <v>23</v>
       </c>
       <c r="H618" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="I618" t="n">
-        <v>0.2163</v>
+        <v>0.2356</v>
       </c>
       <c r="J618" t="n">
-        <v>4.9749</v>
+        <v>5.4188</v>
       </c>
     </row>
     <row r="619">
@@ -28949,10 +28949,10 @@
         <v>0.98</v>
       </c>
       <c r="I619" t="n">
-        <v>-0.0416</v>
+        <v>-0.0418</v>
       </c>
       <c r="J619" t="n">
-        <v>-0.9568</v>
+        <v>-0.9614</v>
       </c>
     </row>
     <row r="620">
@@ -28986,13 +28986,13 @@
         <v>23</v>
       </c>
       <c r="H620" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="I620" t="n">
-        <v>-0.1782</v>
+        <v>-0.1679</v>
       </c>
       <c r="J620" t="n">
-        <v>-4.0986</v>
+        <v>-3.8617</v>
       </c>
     </row>
     <row r="621">
@@ -29026,13 +29026,13 @@
         <v>23</v>
       </c>
       <c r="H621" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="I621" t="n">
-        <v>-0.2099</v>
+        <v>-0.2</v>
       </c>
       <c r="J621" t="n">
-        <v>-4.8277</v>
+        <v>-4.6</v>
       </c>
     </row>
     <row r="622">
@@ -30466,13 +30466,13 @@
         <v>19</v>
       </c>
       <c r="H657" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="I657" t="n">
-        <v>0.6157</v>
+        <v>0.6318</v>
       </c>
       <c r="J657" t="n">
-        <v>11.6983</v>
+        <v>12.0042</v>
       </c>
     </row>
     <row r="658">
@@ -30509,10 +30509,10 @@
         <v>0.89</v>
       </c>
       <c r="I658" t="n">
-        <v>-0.1432</v>
+        <v>-0.1434</v>
       </c>
       <c r="J658" t="n">
-        <v>-2.7208</v>
+        <v>-2.7246</v>
       </c>
     </row>
     <row r="659">
@@ -30549,10 +30549,10 @@
         <v>0.78</v>
       </c>
       <c r="I659" t="n">
-        <v>-0.2545</v>
+        <v>-0.2547</v>
       </c>
       <c r="J659" t="n">
-        <v>-4.8355</v>
+        <v>-4.8393</v>
       </c>
     </row>
     <row r="660">
@@ -30589,10 +30589,10 @@
         <v>0.61</v>
       </c>
       <c r="I660" t="n">
-        <v>-0.411</v>
+        <v>-0.4113</v>
       </c>
       <c r="J660" t="n">
-        <v>-7.809</v>
+        <v>-7.8147</v>
       </c>
     </row>
     <row r="661">
@@ -30629,10 +30629,10 @@
         <v>0.54</v>
       </c>
       <c r="I661" t="n">
-        <v>-0.4727</v>
+        <v>-0.4729</v>
       </c>
       <c r="J661" t="n">
-        <v>-8.981299999999999</v>
+        <v>-8.985099999999999</v>
       </c>
     </row>
   </sheetData>
